--- a/fund.xlsx
+++ b/fund.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -582,56 +582,56 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>58.62</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.42</v>
+        <v>-1.2</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.61</v>
+        <v>-2.25</v>
       </c>
       <c r="F3" t="n">
-        <v>2.15</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.79</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.859999999999999</v>
+        <v>-6.640000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.050000000000001</v>
+        <v>-1.970000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>17.6</v>
+        <v>17.36</v>
       </c>
       <c r="K3" t="n">
-        <v>18.36</v>
+        <v>20.54</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-2.09</v>
+        <v>-2.86</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-3.21</v>
       </c>
       <c r="O3" t="n">
-        <v>2.87</v>
+        <v>2.48</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-15</v>
+        <v>-13.12</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-12.07</v>
+        <v>-13.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>21.11</v>
+        <v>20.84</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.829999999999999</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="4">
@@ -651,56 +651,56 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-2.03</v>
+        <v>-1.94</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-3.12</v>
+        <v>-4.31</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>-7.37</v>
+        <v>5.79</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-5.15</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-15.51</v>
+        <v>-15.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.32</v>
+        <v>-5.950000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>40.26</v>
+        <v>44.79</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-2.6</v>
+        <v>-3.600000000000001</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-5.27</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>8.040000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-20.58</v>
+        <v>-18.53</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-21.72</v>
+        <v>-22.46</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.76</v>
+        <v>-3.18</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>23.11</v>
+        <v>22.78</v>
       </c>
       <c r="T4" t="n">
-        <v>19.07</v>
+        <v>23.13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>159928</t>
         </is>
@@ -716,52 +716,52 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-2.32</v>
+        <v>-2.72</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-5.680000000000001</v>
+        <v>-4.77</v>
       </c>
       <c r="F5" t="n">
-        <v>2.88</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-12.76</v>
+        <v>-10.75</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-21.74</v>
+        <v>-22.17</v>
       </c>
       <c r="I5" t="n">
-        <v>-9.56</v>
+        <v>-11.07</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.68</v>
+        <v>-3.879999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.470000000000001</v>
+        <v>-5.109999999999999</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-3.41</v>
+        <v>-4.38</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-5.16</v>
+        <v>-5.73</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-25.97</v>
+        <v>-24.13</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-27.95</v>
+        <v>-28.67</v>
       </c>
       <c r="R5" t="n">
-        <v>-7</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.17</v>
+        <v>-0.4000000000000004</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-25.66</v>
+        <v>-26.77</v>
       </c>
     </row>
     <row r="6">
@@ -780,53 +780,53 @@
           <t>40.62</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>-0.2699999999999998</v>
+      <c r="D6" s="2" t="n">
+        <v>1.74</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.92</v>
+        <v>-1.31</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.95</v>
+        <v>-3.74</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>12.94</v>
+        <v>11.17</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>27.94</v>
+        <v>29.3</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4199999999999999</v>
+        <v>2.299999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.859999999999999</v>
+        <v>-8.349999999999998</v>
       </c>
       <c r="K6" t="n">
-        <v>21.59</v>
+        <v>21.93</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.36</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4</v>
+        <v>-2.27</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.23</v>
+        <v>-0.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2699999999999996</v>
+        <v>-2.209999999999999</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>21.73</v>
+        <v>22.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.98</v>
+        <v>5.069999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.35</v>
+        <v>-4.869999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4000000000000004</v>
+        <v>0.2699999999999996</v>
       </c>
     </row>
     <row r="7">
@@ -845,26 +845,26 @@
           <t>121.84</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>2.29</v>
+      <c r="D7" t="n">
+        <v>0.29</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4.359999999999999</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>-1.71</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.969999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>28.05</v>
+        <v>27.88</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-20.87</v>
+        <v>-19.08</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-22.84</v>
+        <v>-22.77</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -872,25 +872,25 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.2</v>
+        <v>-1.37</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.33</v>
+        <v>-2.67</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-5.069999999999999</v>
+        <v>9.65</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>-6.41</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>21.84</v>
+        <v>21.38</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-18.31</v>
+        <v>-16.31</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-19.33</v>
+        <v>-19.29</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -901,12 +901,12 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>110020</t>
+          <t>510310</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>易方达沪深300ETF联接A</t>
+          <t>沪深300ETF易方达</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -915,63 +915,63 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.09999999999999987</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08999999999999986</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2800000000000002</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.229999999999997</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5700000000000003</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8200000000000003</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-1.19</v>
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>-1.66</v>
       </c>
       <c r="N8" t="n">
-        <v>0.53</v>
+        <v>-0.96</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.78</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-13.49</v>
+        <v>-13.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>-7.439999999999998</v>
+        <v>-6.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.76</v>
+        <v>2.77</v>
       </c>
       <c r="S8" t="n">
-        <v>4.08</v>
+        <v>3.479999999999999</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-20.37</v>
+        <v>-21.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>007029</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>易方达中证500ETF联接发起式C</t>
+          <t>中证500ETF易方达</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -979,711 +979,646 @@
           <t>4332.99</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>0.9300000000000002</v>
+      <c r="D9" s="2" t="n">
+        <v>1.66</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.47</v>
+        <v>0.96</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6400000000000001</v>
+        <v>-2.78</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>12.14</v>
+        <v>13.38</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.48</v>
+        <v>-2.77</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.19</v>
+        <v>-3.479999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>20.97</v>
+        <v>21.66</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1600000000000001</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05000000000000004</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08000000000000007</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.07</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.710000000000001</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.9199999999999999</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3200000000000003</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2199999999999989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>110026</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>040046</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>易方达创业板ETF联接A</t>
+          <t>华安纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2521.21</t>
+          <t>418.53</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>4.84</v>
+        <v>3.69</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.89</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2800000000000002</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>29.85</v>
+        <v>-1.33</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.289999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.830000000000001</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-13.29</v>
+        <v>-7.380000000000001</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>48.18000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6300000000000008</v>
+        <v>11.29</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>5.36</v>
+        <v>2.029999999999999</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4399999999999999</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-4.489999999999998</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>23.64</v>
+        <v>1.45</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>-16.67</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.789999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7299999999999995</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>-20.56</v>
+        <v>-4.609999999999999</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-10.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>040046</t>
+          <t>050025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>华安纳斯达克100ETF联接(QDII)A</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>418.53</t>
+          <t>619.61</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2.88</v>
+        <v>1.899999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1.12</v>
+        <v>-0.71</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.91</v>
+        <v>-1.31</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.53</v>
+        <v>-1.640000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>8.990000000000002</v>
+        <v>0.1899999999999977</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.800000000000001</v>
+        <v>-3.630000000000001</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>50.28</v>
+        <v>34.28</v>
       </c>
       <c r="K11" t="n">
-        <v>8.379999999999999</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>1.79</v>
+        <v>18.73</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2399999999999993</v>
       </c>
       <c r="N11" t="n">
-        <v>1.64</v>
+        <v>-1.67</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.19</v>
+        <v>1.47</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-16.74</v>
+        <v>-15.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.780000000000001</v>
+        <v>-6.310000000000002</v>
       </c>
       <c r="R11" t="n">
-        <v>-5.24</v>
+        <v>-0.8600000000000003</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>53.79</v>
+        <v>37.76</v>
       </c>
       <c r="T11" t="n">
-        <v>-12.81</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>050025</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>012805</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>广发恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>619.61</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
+          <t>655.24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2.43</v>
       </c>
       <c r="E12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-2.01</v>
+        <v>-2.94</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-12.35</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-10.39</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3200000000000003</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-3.550000000000001</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>35.65000000000001</v>
-      </c>
-      <c r="K12" t="n">
-        <v>15.54</v>
+        <v>-5.350000000000001</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
       <c r="M12" t="n">
-        <v>-0.0900000000000003</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-1.93</v>
+        <v>0.7699999999999996</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>-9.57</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>-15.22</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-5.890000000000001</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-0.9900000000000002</v>
-      </c>
-      <c r="S12" s="2" t="n">
-        <v>39.16</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-5.649999999999999</v>
+        <v>-23.77</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>-11.85</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-2.770000000000001</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>012805</t>
+          <t>000216</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>广发恒生科技ETF联接(QDII)C</t>
+          <t>华安黄金ETF联接A</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>655.24</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-11.62</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>-6.15</v>
+          <t>1947.62</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.83</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.089999999999998</v>
+        <v>0.4100000000000001</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>36.68</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-7.039999999999999</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>-10.9</v>
+        <v>27.25</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>37.59</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.43</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-19.36</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>-14.3</v>
+        <v>-9.549999999999999</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-6.09</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>39.23999999999999</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-3.529999999999999</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>30.02</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="T13" t="n">
+        <v>11.82</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>000216</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>006476</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>华安黄金ETF联接A</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>1947.62</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>-1.48</v>
+          <t>南方原油C</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>271.58</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-7.25</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-6.11</v>
+        <v>-3.82</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>9.82</v>
+        <v>56.19</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.63</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.020000000000003</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>27.89</v>
+        <v>-1.700000000000001</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>-27.89</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>-24.1</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>37.17</v>
+        <v>24.9</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>30.97</v>
+        <v>71.45</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>-2.57</v>
+        <v>-8.91</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>-5.59</v>
+        <v>-4.779999999999999</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>10.54</v>
+        <v>58.97000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-14.84</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-2.189999999999998</v>
-      </c>
-      <c r="R14" s="2" t="n">
-        <v>30.45</v>
+        <v>-15.08</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>-34.39</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>-21.33</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>40.68</v>
-      </c>
-      <c r="T14" t="n">
-        <v>9.780000000000001</v>
+        <v>28.38</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>49.79</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>006476</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>南方原油C</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>271.58</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>54.03</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-3.55</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>-23.17</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>-27.03</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>25.06</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>70.51000000000001</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>54.75</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>-16.76</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>-29.38</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>-24.47</v>
-      </c>
-      <c r="S15" s="2" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>49.32</v>
-      </c>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>易方达中债新综指发起式(LOF)A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>交银优选回报灵活配置混合C</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>名字</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>基金经理管理规模</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>近一周</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1周~1月</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1月~3月</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3月~6月</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6月~1年</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1年~2年</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2年~3年</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3年~5年</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>交银优选回报灵活配置混合C</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+          <t>近一周</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1周~1月</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1月~3月</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>3月~6月</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>6月~1年</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1年~2年</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2年~3年</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>3年~5年</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>代码</t>
+          <t>011555</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>名字</t>
+          <t>海富通欣利混合C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>基金经理管理规模</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>近一周</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1周~1月</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>1月~3月</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>3月~6月</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>6月~1年</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1年~2年</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2年~3年</t>
-        </is>
+          <t>111.88</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>-7.25</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3年~5年</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>近一周</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1周~1月</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1月~3月</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>3月~6月</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>6月~1年</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>1年~2年</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>2年~3年</t>
-        </is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>0.3800000000000001</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>3年~5年</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr"/>
+          <t>--</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>011555</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>海富通欣利混合C</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>111.88</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>0.08999999999999997</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>0.8899999999999999</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>13.79</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>-7.77</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>-0.96</v>
+          <t>易方达中债新综指发起式(LOF)A</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>832.63</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0.29</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.9299999999999999</v>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="Q21" s="2" t="n">
-        <v>11.1</v>
+        <v>0.41</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>-0.6699999999999999</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>-2.79</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-0.04000000000000004</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>161119</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>842.65</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.04000000000000004</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>-2.69</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="S22" s="2" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.350000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1697,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -1854,20 +1789,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>110026</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>易方达创业板ETF联接A</t>
+          <t>中证500ETF易方达</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.7326</v>
+        <v>1.636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1879,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>69.62</v>
+        <v>61.63</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1898,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>113.35</v>
+        <v>109.05</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1917,7 +1852,7 @@
         <v>-1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.0477</v>
+        <v>0.9752</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -1928,7 +1863,7 @@
         <v>-1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>17.1</v>
+        <v>16.5</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1936,13 +1871,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>1.563</v>
+        <v>1.223</v>
       </c>
       <c r="W2" t="n">
-        <v>100</v>
+        <v>92.2</v>
       </c>
       <c r="X2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1955,7 +1890,7 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>54.99</v>
+        <v>38.31</v>
       </c>
       <c r="AB2" t="n">
         <v>-2.5</v>
@@ -1969,20 +1904,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>050025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>沪深300ETF易方达</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.4229</v>
+        <v>5.3271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1994,15 +1929,15 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>61.11</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2013,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>110.77</v>
+        <v>105.65</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -2032,7 +1967,7 @@
         <v>-1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9345</v>
+        <v>0.9439</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2040,21 +1975,21 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="T3" t="n">
-        <v>16</v>
+        <v>25.9</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.842</v>
+        <v>0.699</v>
       </c>
       <c r="W3" t="n">
-        <v>80.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="X3" t="n">
         <v>-1</v>
@@ -2070,10 +2005,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>37.6</v>
+        <v>18.73</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -2084,20 +2019,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>007029</t>
+          <t>501060</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>易方达中证500ETF联接发起式C</t>
+          <t>中金中证优选300指数(LOF)A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.9297</v>
+        <v>2.3964</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2109,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>59.54</v>
+        <v>52.84</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2128,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>110.76</v>
+        <v>99.81</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2140,14 +2075,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9711</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2158,7 +2093,7 @@
         <v>-1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>16.1</v>
+        <v>12.3</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -2166,29 +2101,29 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>1.197</v>
+        <v>0.664</v>
       </c>
       <c r="W4" t="n">
-        <v>90.5</v>
+        <v>93.2</v>
       </c>
       <c r="X4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>36.5</v>
+        <v>24.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -2199,32 +2134,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>050025</t>
+          <t>159928</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>消费ETF汇添富</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.267</v>
+        <v>2.966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>68.90000000000001</v>
+        <v>41.38</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2243,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>104.25</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -2255,25 +2190,25 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9296</v>
+        <v>0.249</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>24</v>
+        <v>14.1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2281,29 +2216,29 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.68</v>
+        <v>0.768</v>
       </c>
       <c r="W5" t="n">
-        <v>98.59999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>18.73</v>
+        <v>51.23</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2.5</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -2314,20 +2249,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>510310</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>交银优选回报灵活配置混合C</t>
+          <t>沪深300ETF易方达</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.5483</v>
+        <v>2.4368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2339,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>64.18000000000001</v>
+        <v>63.05</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2358,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>109.64</v>
+        <v>109.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2377,7 +2312,7 @@
         <v>-1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9414</v>
+        <v>0.9409</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2388,7 +2323,7 @@
         <v>-1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>17.7</v>
+        <v>16.7</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -2396,13 +2331,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>99.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2415,7 +2350,7 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>3.91</v>
+        <v>37.4</v>
       </c>
       <c r="AB6" t="n">
         <v>-2.5</v>
@@ -2429,16 +2364,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>510580</t>
+          <t>006476</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中证500ETF易方达</t>
+          <t>南方原油C</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.6212</v>
+        <v>1.5723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2454,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>59.49</v>
+        <v>45.57</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2473,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>110.75</v>
+        <v>-3.85</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2485,39 +2420,39 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9724</v>
+        <v>-0.0072</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>-1.5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>16</v>
+        <v>26.7</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.259</v>
+        <v>3.017</v>
       </c>
       <c r="W7" t="n">
-        <v>90.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2530,34 +2465,34 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>38.31</v>
+        <v>31.68</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>持有</t>
+        <v>4</v>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>040046</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>华安纳斯达克100ETF联接(QDII)A</t>
+          <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.5222</v>
+        <v>1.7764</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2569,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>72.44</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2577,7 +2512,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -2588,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>105.34</v>
+        <v>100.17</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2607,7 +2542,7 @@
         <v>-1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9619</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2615,21 +2550,21 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="T8" t="n">
-        <v>23.4</v>
+        <v>53.7</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.978</v>
+        <v>0.042</v>
       </c>
       <c r="W8" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="X8" t="n">
         <v>-1</v>
@@ -2645,34 +2580,34 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>31.24</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>卖出</t>
+        <v>-1</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>持有</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>040046</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>消费ETF汇添富</t>
+          <t>华安纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.9664</v>
+        <v>7.6436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2684,15 +2619,15 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>41.43</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -2703,64 +2638,64 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>24.84</v>
+        <v>106.44</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>-1</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0.2545</v>
+        <v>1.0041</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T9" t="n">
-        <v>13.9</v>
+        <v>25.5</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.826</v>
+        <v>1.006</v>
       </c>
       <c r="W9" t="n">
-        <v>9.800000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>51.23</v>
+        <v>31.24</v>
       </c>
       <c r="AB9" t="n">
         <v>-1</v>
@@ -2774,20 +2709,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>006476</t>
+          <t>012805</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>南方原油C</t>
+          <t>广发恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.6762</v>
+        <v>0.8186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2799,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>54.02</v>
+        <v>56.16</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -2818,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>12.04</v>
+        <v>106.06</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2830,55 +2765,55 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3813</v>
+        <v>0.9583</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>28.1</v>
+        <v>18.9</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>2.571</v>
+        <v>1.409</v>
       </c>
       <c r="W10" t="n">
-        <v>91.7</v>
+        <v>52.2</v>
       </c>
       <c r="X10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>31.68</v>
+        <v>53.89</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -2898,11 +2833,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.6524</v>
+        <v>3.6563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2914,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>49.56</v>
+        <v>49.83</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2933,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>87.23</v>
+        <v>81.03</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2952,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7123</v>
+        <v>0.7133</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2963,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2971,10 +2906,10 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1.513</v>
+        <v>1.411</v>
       </c>
       <c r="W11" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -3004,20 +2939,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>012805</t>
+          <t>008115</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>广发恒生科技ETF联接(QDII)C</t>
+          <t>天弘中证红利低波动100联接C</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.8154</v>
+        <v>1.7583</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3029,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>55.27</v>
+        <v>44.48</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -3048,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>108.59</v>
+        <v>44.59</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3060,25 +2995,25 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9769</v>
+        <v>0.3396</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>19.4</v>
+        <v>11.8</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -3086,10 +3021,10 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1.493</v>
+        <v>0.46</v>
       </c>
       <c r="W12" t="n">
-        <v>51.6</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -3105,10 +3040,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>53.89</v>
+        <v>13.26</v>
       </c>
       <c r="AB12" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -3119,20 +3054,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501060</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中金中证优选300指数(LOF)A</t>
+          <t>交银优选回报灵活配置混合C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.3873</v>
+        <v>1.5491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3144,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>50.83</v>
+        <v>65.77</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3163,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>101.3</v>
+        <v>107.61</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3182,18 +3117,18 @@
         <v>-1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7945</v>
+        <v>0.9321</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>12.8</v>
+        <v>18.7</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3201,29 +3136,29 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="W13" t="n">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="X13" t="n">
         <v>-1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>24.8</v>
+        <v>3.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -3243,11 +3178,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.612</v>
+        <v>2.664</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3259,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>56.02</v>
+        <v>60.97</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3278,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>110.94</v>
+        <v>109.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3297,7 +3232,7 @@
         <v>-1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8858</v>
+        <v>1.0117</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -3308,7 +3243,7 @@
         <v>-1.5</v>
       </c>
       <c r="T14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3316,17 +3251,17 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1.209</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="X14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -3358,11 +3293,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7467</v>
+        <v>0.7488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3374,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>59.13</v>
+        <v>59.71</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3393,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>119.06</v>
+        <v>117.27</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3412,7 +3347,7 @@
         <v>-1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.8343</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -3423,7 +3358,7 @@
         <v>-1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3431,10 +3366,10 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1.501</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -3464,20 +3399,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>008115</t>
+          <t>011555</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>天弘中证红利低波动100联接C</t>
+          <t>海富通欣利混合C</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.7567</v>
+        <v>1.4454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3489,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>43.68</v>
+        <v>55.76</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -3508,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>46.62</v>
+        <v>106.27</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3520,25 +3455,25 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2931</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T16" t="n">
-        <v>11.8</v>
+        <v>14.1</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -3546,13 +3481,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.488</v>
+        <v>0.35</v>
       </c>
       <c r="W16" t="n">
-        <v>92.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -3561,361 +3496,16 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>13.26</v>
+        <v>12.06</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AC16" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>011555</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>海富通欣利混合C</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1.443</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>54.21</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>105.23</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.8645</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="W17" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="AA17" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>110020</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>易方达沪深300ETF联接A</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1.9016</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>61.16</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>110.79</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.9347</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="W18" t="n">
-        <v>82</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="AA18" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>161119</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1.7761</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>86.47</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.0065</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>趋势</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="W19" t="n">
-        <v>100</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC19" t="inlineStr">
         <is>
           <t>持有</t>
         </is>

--- a/fund.xlsx
+++ b/fund.xlsx
@@ -1789,20 +1789,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>510580</t>
+          <t>050025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中证500ETF易方达</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.636</v>
+        <v>5.3244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1814,15 +1814,15 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>61.63</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>109.05</v>
+        <v>105.65</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>-1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9752</v>
+        <v>0.9404</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -1860,24 +1860,24 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="T2" t="n">
-        <v>16.5</v>
+        <v>25.8</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>1.223</v>
+        <v>0.696</v>
       </c>
       <c r="W2" t="n">
-        <v>92.2</v>
+        <v>100</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>38.31</v>
+        <v>18.73</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -1904,20 +1904,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>050025</t>
+          <t>008115</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>天弘中证红利低波动100联接C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.3271</v>
+        <v>1.7711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1929,26 +1929,26 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>72.23999999999999</v>
+        <v>50.51</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>105.65</v>
+        <v>91.47</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1960,55 +1960,55 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9439</v>
+        <v>0.5607</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>25.9</v>
+        <v>11</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.699</v>
+        <v>0.475</v>
       </c>
       <c r="W3" t="n">
-        <v>100</v>
+        <v>93.7</v>
       </c>
       <c r="X3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>18.73</v>
+        <v>13.26</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -2019,20 +2019,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>501060</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中金中证优选300指数(LOF)A</t>
+          <t>交银优选回报灵活配置混合C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.3964</v>
+        <v>1.5491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>52.84</v>
+        <v>65.77</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>99.81</v>
+        <v>105.87</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2075,14 +2075,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8915</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>-1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>12.3</v>
+        <v>19.6</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -2101,29 +2101,29 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.664</v>
+        <v>0.077</v>
       </c>
       <c r="W4" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>24.8</v>
+        <v>3.91</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1.5</v>
+        <v>-2.5</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -2134,32 +2134,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>011555</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>消费ETF汇添富</t>
+          <t>海富通欣利混合C</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.966</v>
+        <v>1.4463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>41.38</v>
+        <v>56.36</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.18</v>
+        <v>106.54</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -2190,25 +2190,25 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.249</v>
+        <v>0.8821</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2216,29 +2216,29 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.768</v>
+        <v>0.329</v>
       </c>
       <c r="W5" t="n">
-        <v>9.800000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>51.23</v>
+        <v>12.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>-2.5</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>012832</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>沪深300ETF易方达</t>
+          <t>南方中证新能源ETF联接C</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.4368</v>
+        <v>0.7572</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>63.05</v>
+        <v>62.03</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>109.6</v>
+        <v>114.55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>-1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9409</v>
+        <v>0.8784</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>-1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>16.7</v>
+        <v>14.7</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.8179999999999999</v>
+        <v>1.374</v>
       </c>
       <c r="W6" t="n">
-        <v>81.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>37.4</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AB6" t="n">
         <v>-2.5</v>
@@ -2364,20 +2364,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>006476</t>
+          <t>000216</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南方原油C</t>
+          <t>华安黄金ETF联接A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.5723</v>
+        <v>3.6461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>45.57</v>
+        <v>49.08</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2408,91 +2408,91 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.85</v>
+        <v>70.97</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0072</v>
+        <v>0.6967</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>26.7</v>
+        <v>9.6</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>3.017</v>
+        <v>1.334</v>
       </c>
       <c r="W7" t="n">
-        <v>84.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
       <c r="AA7" t="n">
-        <v>31.68</v>
+        <v>25.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>买入</t>
+        <v>-1</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>持有</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
+          <t>中证500ETF易方达</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.7764</v>
+        <v>1.6326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2504,15 +2504,15 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>86.84999999999999</v>
+        <v>60.83</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>100.17</v>
+        <v>103.89</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>-1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9619</v>
+        <v>0.9131</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2550,24 +2550,24 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>53.7</v>
+        <v>16.9</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.042</v>
+        <v>1.153</v>
       </c>
       <c r="W8" t="n">
-        <v>100</v>
+        <v>91.8</v>
       </c>
       <c r="X8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>38.31</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -2603,11 +2603,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.6436</v>
+        <v>7.5296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>75.48999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>106.44</v>
+        <v>100.47</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>-1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.0041</v>
+        <v>0.9307</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2665,21 +2665,21 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>25.5</v>
+        <v>24.9</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1.006</v>
+        <v>0.954</v>
       </c>
       <c r="W9" t="n">
-        <v>99.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="X9" t="n">
         <v>-1</v>
@@ -2698,7 +2698,7 @@
         <v>31.24</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -2709,20 +2709,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>012805</t>
+          <t>006476</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>广发恒生科技ETF联接(QDII)C</t>
+          <t>南方原油C</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8186</v>
+        <v>1.5723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>56.16</v>
+        <v>45.57</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>106.06</v>
+        <v>-3.85</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2765,79 +2765,79 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9583</v>
+        <v>-0.0072</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>-1.5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>18.9</v>
+        <v>26.7</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>1.409</v>
+        <v>3.017</v>
       </c>
       <c r="W10" t="n">
-        <v>52.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>53.89</v>
+        <v>31.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>持有</t>
+        <v>4</v>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>000216</t>
+          <t>012805</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>华安黄金ETF联接A</t>
+          <t>广发恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.6563</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>49.83</v>
+        <v>55.57</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>81.03</v>
+        <v>100.27</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2880,25 +2880,25 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7133</v>
+        <v>0.8861</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>10.2</v>
+        <v>18.3</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1.411</v>
+        <v>1.324</v>
       </c>
       <c r="W11" t="n">
-        <v>79.2</v>
+        <v>51.9</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -2921,14 +2921,14 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>25.07</v>
+        <v>53.89</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -2939,20 +2939,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>008115</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天弘中证红利低波动100联接C</t>
+          <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.7583</v>
+        <v>1.7771</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2964,15 +2964,15 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>44.48</v>
+        <v>87.73</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>44.59</v>
+        <v>100.45</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2995,55 +2995,55 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3396</v>
+        <v>0.9504</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T12" t="n">
-        <v>11.8</v>
+        <v>55.3</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.46</v>
+        <v>0.042</v>
       </c>
       <c r="W12" t="n">
-        <v>92.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>13.26</v>
+        <v>1.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -3054,20 +3054,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>515580</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>交银优选回报灵活配置混合C</t>
+          <t>科技100ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.5491</v>
+        <v>2.6485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>65.77</v>
+        <v>58.84</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>107.61</v>
+        <v>100.03</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>-1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9321</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>-1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>18.7</v>
+        <v>15.7</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.083</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>100</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>3.91</v>
+        <v>38.9</v>
       </c>
       <c r="AB13" t="n">
         <v>-2.5</v>
@@ -3169,20 +3169,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>515580</t>
+          <t>501060</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>科技100ETF华泰柏瑞</t>
+          <t>中金中证优选300指数(LOF)A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.664</v>
+        <v>2.4033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>60.97</v>
+        <v>54.36</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>109.9</v>
+        <v>104.36</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>-1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.0117</v>
+        <v>0.9129</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>-1.5</v>
       </c>
       <c r="T14" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3251,26 +3251,26 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1.24</v>
+        <v>0.635</v>
       </c>
       <c r="W14" t="n">
-        <v>93</v>
+        <v>93.7</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>38.9</v>
+        <v>24.8</v>
       </c>
       <c r="AB14" t="n">
         <v>-2.5</v>
@@ -3284,32 +3284,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>012832</t>
+          <t>159928</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>南方中证新能源ETF联接C</t>
+          <t>消费ETF汇添富</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7488</v>
+        <v>2.9716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>59.71</v>
+        <v>42.47</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>117.27</v>
+        <v>0.26</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3340,55 +3340,55 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="W15" t="n">
+        <v>10</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="AB15" t="n">
         <v>-1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.8343</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>14</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W15" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="AA15" t="n">
-        <v>65.01000000000001</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-2.5</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3399,20 +3399,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>011555</t>
+          <t>510310</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>海富通欣利混合C</t>
+          <t>沪深300ETF易方达</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.4454</v>
+        <v>2.4392</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3424,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>55.76</v>
+        <v>63.39</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>106.27</v>
+        <v>108.01</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>-1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.9031</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>-1.5</v>
       </c>
       <c r="T16" t="n">
-        <v>14.1</v>
+        <v>17.4</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -3481,17 +3481,17 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.35</v>
+        <v>0.766</v>
       </c>
       <c r="W16" t="n">
-        <v>94.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>12.06</v>
+        <v>37.4</v>
       </c>
       <c r="AB16" t="n">
         <v>-2.5</v>

--- a/fund.xlsx
+++ b/fund.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -582,56 +582,56 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>58.62</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>-1.2</v>
+          <t>61.62</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>-2.08</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.25</v>
+        <v>-2.16</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2999999999999998</v>
+        <v>0.3500000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2599999999999998</v>
+        <v>-0.01000000000000023</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.640000000000001</v>
+        <v>-6.870000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.970000000000001</v>
+        <v>-1.479999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>17.36</v>
+        <v>16.19</v>
       </c>
       <c r="K3" t="n">
-        <v>20.54</v>
+        <v>21.05</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>-2.86</v>
+        <v>-3.76</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-3.21</v>
+        <v>-3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>2.48</v>
+        <v>4.6</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-13.12</v>
+        <v>-15.49</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-13.14</v>
+        <v>-12.01</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7999999999999998</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>20.84</v>
+        <v>-0.1499999999999986</v>
+      </c>
+      <c r="S3" t="n">
+        <v>19.77</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.12</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="4">
@@ -645,58 +645,58 @@
           <t>天弘中证红利低波动100联接C</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>59.17</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>131.60</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-1.94</v>
+        <v>-2.45</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-4.31</v>
+        <v>-4.33</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5.79</v>
+        <v>6.16</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.15</v>
+        <v>-5.05</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-15.96</v>
+        <v>-16.54</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.950000000000001</v>
+        <v>-4.869999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>19.3</v>
+        <v>17.72</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>44.79</v>
+        <v>45.23</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>-3.600000000000001</v>
+        <v>-4.13</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-5.27</v>
+        <v>-5.42</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>8.57</v>
+        <v>10.41</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-18.53</v>
+        <v>-20.53</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-22.46</v>
+        <v>-21.68</v>
       </c>
       <c r="R4" t="n">
-        <v>-3.18</v>
+        <v>-3.539999999999999</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>22.78</v>
+        <v>21.3</v>
       </c>
       <c r="T4" t="n">
-        <v>23.13</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="5">
@@ -712,56 +712,56 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>580.75</t>
+          <t>553.76</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-2.72</v>
+        <v>-4.51</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-4.77</v>
+        <v>-4.54</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8999999999999999</v>
+        <v>2.57</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-10.75</v>
+        <v>-10.59</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-22.17</v>
+        <v>-23.4</v>
       </c>
       <c r="I5" t="n">
-        <v>-11.07</v>
+        <v>-13.94</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.879999999999999</v>
+        <v>-3.239999999999998</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.109999999999999</v>
+        <v>-4.23</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-4.38</v>
+        <v>-6.19</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-5.73</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.68</v>
+        <v>-5.63</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>6.82</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-24.13</v>
+        <v>-26.07</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-28.67</v>
+        <v>-28.54</v>
       </c>
       <c r="R5" t="n">
-        <v>-8.300000000000001</v>
+        <v>-12.61</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4000000000000004</v>
+        <v>0.3400000000000016</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-26.77</v>
+        <v>-24.76</v>
       </c>
     </row>
     <row r="6">
@@ -775,58 +775,58 @@
           <t>科技100ETF华泰柏瑞</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>40.62</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>101.98</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.31</v>
+        <v>-0.7799999999999998</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.74</v>
+        <v>-3.77</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>11.17</v>
+        <v>10.05</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>29.3</v>
+        <v>29.45</v>
       </c>
       <c r="I6" t="n">
-        <v>2.299999999999999</v>
+        <v>3.16</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.349999999999998</v>
+        <v>-7.609999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>21.93</v>
+        <v>19.77</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08000000000000007</v>
+        <v>-0.1500000000000004</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.27</v>
+        <v>-1.87</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.96</v>
+        <v>0.4800000000000004</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.209999999999999</v>
+        <v>-5.429999999999998</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>22.8</v>
+        <v>24.31</v>
       </c>
       <c r="R6" t="n">
-        <v>5.069999999999999</v>
+        <v>4.49</v>
       </c>
       <c r="S6" t="n">
-        <v>-4.869999999999999</v>
+        <v>-4.029999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2699999999999996</v>
+        <v>-0.7600000000000002</v>
       </c>
     </row>
     <row r="7">
@@ -842,29 +842,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>132.24</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.29</v>
+        <v>1.41</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.71</v>
+        <v>-2.58</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6.969999999999999</v>
+        <v>6.16</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>8.860000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>27.88</v>
+        <v>25.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-19.08</v>
+        <v>-18.73</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-22.77</v>
+        <v>-23.95</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -872,25 +872,25 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-1.37</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-2.67</v>
+        <v>-0.27</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-3.67</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>9.65</v>
+        <v>10.41</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>-6.41</v>
+        <v>-6.619999999999997</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>21.38</v>
+        <v>20.76</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-16.31</v>
+        <v>-17.4</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-19.29</v>
+        <v>-20.37</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>4332.99</t>
+          <t>2637.86</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -939,28 +939,28 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>-1.66</v>
+        <v>-1.68</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.96</v>
+        <v>-1.09</v>
       </c>
       <c r="O8" t="n">
-        <v>2.78</v>
+        <v>4.25</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-13.38</v>
+        <v>-15.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.5</v>
+        <v>-5.140000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>2.77</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.479999999999999</v>
+        <v>3.58</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-21.66</v>
+        <v>-20.53</v>
       </c>
     </row>
     <row r="9">
@@ -976,32 +976,32 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>4332.99</t>
+          <t>2637.86</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="E9" t="n">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.78</v>
+        <v>-4.25</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>13.38</v>
+        <v>15.48</v>
       </c>
       <c r="H9" t="n">
-        <v>6.5</v>
+        <v>5.140000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.77</v>
+        <v>-1.33</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.479999999999999</v>
+        <v>-3.58</v>
       </c>
       <c r="K9" t="n">
-        <v>21.66</v>
+        <v>20.53</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1041,56 +1041,56 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>418.53</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.89</v>
+          <t>380.36</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.06999999999999984</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4.960000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.33</v>
+        <v>-3.87</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="H10" t="n">
-        <v>9.289999999999999</v>
+        <v>-4.27</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>13.08</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.380000000000001</v>
+        <v>-7.829999999999999</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>48.18000000000001</v>
+        <v>43.91</v>
       </c>
       <c r="K10" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>2.029999999999999</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-1.85</v>
+        <v>13.61</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>3.87</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>0.3799999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-16.67</v>
+        <v>-19.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.789999999999999</v>
+        <v>7.939999999999998</v>
       </c>
       <c r="R10" t="n">
-        <v>-4.609999999999999</v>
+        <v>-6.499999999999999</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>51.66</v>
+        <v>47.49</v>
       </c>
       <c r="T10" t="n">
-        <v>-10.37</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="11">
@@ -1106,56 +1106,56 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>619.61</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>1.899999999999999</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.71</v>
+          <t>572.21</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>3.72</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.31</v>
+        <v>-3.22</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.640000000000001</v>
+        <v>-2.47</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1899999999999977</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.630000000000001</v>
+        <v>-5.709999999999999</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>34.28</v>
+        <v>31.91</v>
       </c>
       <c r="K11" t="n">
-        <v>18.73</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2399999999999993</v>
+        <v>20.84</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>-2.83</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.67</v>
+        <v>2.63</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.03</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-15.02</v>
+        <v>-17.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.310000000000002</v>
+        <v>-1.890000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.8600000000000003</v>
+        <v>-4.379999999999999</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>37.76</v>
+        <v>35.49</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.93</v>
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1171,55 +1171,55 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>655.24</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>2.43</v>
+          <t>509.35</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.45</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.94</v>
+        <v>-2.14</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-12.35</v>
+        <v>-13.41</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-10.39</v>
+        <v>-7.710000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.350000000000001</v>
+        <v>-7.050000000000001</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>38.77</v>
+        <v>36.01000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.25</v>
+        <v>-3.66</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>0.7699999999999996</v>
+      <c r="M12" s="3" t="n">
+        <v>-3.13</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>-3.9</v>
+        <v>-3.23</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>-9.57</v>
+        <v>-9.16</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>-23.77</v>
+        <v>-23.19</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>-11.85</v>
+        <v>-12.19</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>41.54</v>
+        <v>37.34</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.770000000000001</v>
+        <v>-0.08000000000000007</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1230,395 +1230,659 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>000216</t>
+          <t>000369</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>华安黄金ETF联接A</t>
+          <t>广发全球医疗保健指数人民币(QDII)A</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>1947.62</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>-1.28</v>
+          <t>1071.35</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-4.3</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.66</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.65</v>
+        <v>0.4399999999999999</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-4.909999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.4100000000000001</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>37.59</v>
+        <v>2.59</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>-15.63</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-10.32</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13.59</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>33.48</v>
+        <v>35.02</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-2.94</v>
+        <v>-5.98</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.62</v>
+        <v>-0.6500000000000004</v>
       </c>
       <c r="O13" t="n">
-        <v>4.43</v>
+        <v>-0.6599999999999993</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-9.549999999999999</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-6.09</v>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>30.02</v>
-      </c>
-      <c r="S13" s="2" t="n">
-        <v>41.07</v>
+        <v>-12.89</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>-20.77</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-8.989999999999998</v>
+      </c>
+      <c r="S13" t="n">
+        <v>17.17</v>
       </c>
       <c r="T13" t="n">
-        <v>11.82</v>
+        <v>14.49</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>006476</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>118002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>南方原油C</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>271.58</t>
+          <t>易方达标普消费品指数A</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9.80</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-3.82</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>56.19</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-1.700000000000001</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>-27.89</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>-24.1</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>24.9</v>
+        <v>-2.13</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-9.100000000000001</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-8.040000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3399999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-14.91</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.410000000000001</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>71.45</v>
+        <v>27.51</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>-8.91</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>-4.779999999999999</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>58.97000000000001</v>
+        <v>-3.81</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>-4.850000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-15.08</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>-34.39</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>-21.33</v>
-      </c>
-      <c r="S14" s="2" t="n">
-        <v>28.38</v>
-      </c>
-      <c r="T14" s="2" t="n">
-        <v>49.79</v>
+        <v>-23.52</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-4.800000000000001</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-13.58</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5.990000000000001</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6.979999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>159687</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>亚太精选ETF南方</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>294.30</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3000000000000003</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.5699999999999985</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6399999999999997</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>-15.33</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.7300000000000004</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.7600000000000016</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>513880</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>日经225ETF华安</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>380.36</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.3399999999999999</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>5.960000000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.7000000000000002</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8.149999999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-10.41</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.470000000000001</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>-16.18</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.009999999999998</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-9.08</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-18.06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>000216</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>华安黄金ETF联接A</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2131.63</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.7199999999999998</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-4.859999999999998</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>-14</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>36.24</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="T17" t="n">
+        <v>13.16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>006476</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>南方原油C</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>294.30</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.9299999999999997</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-7.85</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>-28.06</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>-23.88</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>71.56</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>-8.940000000000001</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>63.81</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>-15.27</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>-33.2</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>-22.55</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>51.03</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
         <is>
           <t>交银优选回报灵活配置混合C</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>名字</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>基金经理管理规模</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>近一周</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>1周~1月</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>1月~3月</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>3月~6月</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>6月~1年</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>1年~2年</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>2年~3年</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>3年~5年</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>近一周</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>1周~1月</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>1月~3月</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>3月~6月</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>6月~1年</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>1年~2年</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>2年~3年</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>3年~5年</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>011555</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>海富通欣利混合C</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>111.88</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>146.66</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n">
-        <v>0.3800000000000001</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Q20" s="2" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T20" t="inlineStr">
+      <c r="M24" s="2" t="n">
+        <v>0.5599999999999999</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3900000000000001</v>
+      </c>
+      <c r="T24" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>161119</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>832.63</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-0.6699999999999999</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-2.79</v>
-      </c>
-      <c r="R21" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="S21" s="2" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.350000000000001</v>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>794.42</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.03999999999999998</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>-0.6799999999999999</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.69</v>
       </c>
     </row>
   </sheetData>
@@ -1632,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -1789,20 +2053,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>050025</t>
+          <t>159928</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>消费ETF汇添富</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.3244</v>
+        <v>2.9554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1814,15 +2078,15 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>72.09999999999999</v>
+        <v>40.52</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1833,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>105.65</v>
+        <v>-4.43</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1845,55 +2109,55 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9404</v>
+        <v>0.156</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-1</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>25.8</v>
+        <v>15.1</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>0.696</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>100</v>
+        <v>9.5</v>
       </c>
       <c r="X2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>18.73</v>
+        <v>51.23</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -1904,20 +2168,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>008115</t>
+          <t>501060</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>天弘中证红利低波动100联接C</t>
+          <t>中金中证优选300指数(LOF)A</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.7711</v>
+        <v>2.3946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1929,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>50.51</v>
+        <v>52.03</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1941,14 +2205,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>91.47</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1967,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5607</v>
+        <v>0.7603</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1978,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1986,10 +2250,10 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.475</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>93.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -2005,10 +2269,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>13.26</v>
+        <v>24.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -2019,20 +2283,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>040046</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>交银优选回报灵活配置混合C</t>
+          <t>华安纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.5491</v>
+        <v>7.6176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2044,15 +2308,15 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>65.77</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2063,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>105.87</v>
+        <v>100.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2082,7 +2346,7 @@
         <v>-1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8915</v>
+        <v>0.8994</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2090,21 +2354,21 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="T4" t="n">
-        <v>19.6</v>
+        <v>27.3</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.077</v>
+        <v>0.959</v>
       </c>
       <c r="W4" t="n">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="X4" t="n">
         <v>-1</v>
@@ -2120,10 +2384,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>3.91</v>
+        <v>31.24</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -2134,20 +2398,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>011555</t>
+          <t>513880</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>海富通欣利混合C</t>
+          <t>日经225ETF华安</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.4463</v>
+        <v>1.8636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2159,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>56.36</v>
+        <v>63.38</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2178,26 +2442,26 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>106.54</v>
+        <v>92.52</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8821</v>
+        <v>0.8446</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2208,7 +2472,7 @@
         <v>-1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>14</v>
+        <v>18.9</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2216,10 +2480,10 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.329</v>
+        <v>1.487</v>
       </c>
       <c r="W5" t="n">
-        <v>95.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="X5" t="n">
         <v>-1</v>
@@ -2235,10 +2499,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>12.06</v>
+        <v>27.43</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -2249,20 +2513,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>012832</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>南方中证新能源ETF联接C</t>
+          <t>交银优选回报灵活配置混合C</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7572</v>
+        <v>1.5492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2274,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>62.03</v>
+        <v>63.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2293,26 +2557,26 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>114.55</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8784</v>
+        <v>0.8056</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2323,7 +2587,7 @@
         <v>-1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>14.7</v>
+        <v>21.4</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -2331,13 +2595,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.374</v>
+        <v>0.079</v>
       </c>
       <c r="W6" t="n">
-        <v>51.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2350,7 +2614,7 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>65.01000000000001</v>
+        <v>3.91</v>
       </c>
       <c r="AB6" t="n">
         <v>-2.5</v>
@@ -2364,20 +2628,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>000216</t>
+          <t>012832</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>华安黄金ETF联接A</t>
+          <t>南方中证新能源ETF联接C</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.6461</v>
+        <v>0.7446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2389,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>49.08</v>
+        <v>56.31</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2408,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>70.97</v>
+        <v>73.67</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2427,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6967</v>
+        <v>0.712</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2438,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>9.6</v>
+        <v>15.2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2446,17 +2710,17 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.334</v>
+        <v>1.335</v>
       </c>
       <c r="W7" t="n">
-        <v>78.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2465,7 +2729,7 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>25.07</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AB7" t="n">
         <v>-1</v>
@@ -2479,20 +2743,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>510580</t>
+          <t>515580</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中证500ETF易方达</t>
+          <t>科技100ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.6326</v>
+        <v>2.6622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2504,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>60.83</v>
+        <v>58.56</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2523,26 +2787,26 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>103.89</v>
+        <v>84.44</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9131</v>
+        <v>0.8331</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2553,7 +2817,7 @@
         <v>-1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -2561,10 +2825,10 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.153</v>
+        <v>1.214</v>
       </c>
       <c r="W8" t="n">
-        <v>91.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -2580,7 +2844,7 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>38.31</v>
+        <v>38.9</v>
       </c>
       <c r="AB8" t="n">
         <v>-2.5</v>
@@ -2594,20 +2858,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>040046</t>
+          <t>000216</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>华安纳斯达克100ETF联接(QDII)A</t>
+          <t>华安黄金ETF联接A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.5296</v>
+        <v>3.5941</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2619,15 +2883,15 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>71.59999999999999</v>
+        <v>45.14</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -2638,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>100.47</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2650,25 +2914,25 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9307</v>
+        <v>0.4856</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>24.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2676,29 +2940,29 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.954</v>
+        <v>1.268</v>
       </c>
       <c r="W9" t="n">
-        <v>97.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="X9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
       <c r="AA9" t="n">
-        <v>31.24</v>
+        <v>25.07</v>
       </c>
       <c r="AB9" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -2709,20 +2973,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>006476</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>南方原油C</t>
+          <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.5723</v>
+        <v>1.779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2734,15 +2998,15 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>45.57</v>
+        <v>87.56</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -2753,37 +3017,37 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.85</v>
+        <v>98.36</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.0072</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T10" t="n">
-        <v>26.7</v>
+        <v>58.5</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2791,13 +3055,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>3.017</v>
+        <v>0.046</v>
       </c>
       <c r="W10" t="n">
-        <v>84.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2810,14 +3074,14 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>31.68</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>买入</t>
+        <v>-1</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>持有</t>
         </is>
       </c>
     </row>
@@ -2833,11 +3097,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.7852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2849,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>55.57</v>
+        <v>44.97</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2868,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>100.27</v>
+        <v>21.09</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2880,25 +3144,25 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8861</v>
+        <v>0.4932</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>18.3</v>
+        <v>16.6</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2906,10 +3170,10 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1.324</v>
+        <v>1.468</v>
       </c>
       <c r="W11" t="n">
-        <v>51.9</v>
+        <v>46.6</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -2928,7 +3192,7 @@
         <v>53.89</v>
       </c>
       <c r="AB11" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -2939,16 +3203,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>159687</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
+          <t>亚太精选ETF南方</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.7771</v>
+        <v>1.7274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2964,70 +3228,70 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>87.73</v>
+        <v>61.42</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.8836000000000001</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>100.45</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.9504</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
       <c r="S12" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>55.3</v>
+        <v>16.6</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.042</v>
+        <v>1.457</v>
       </c>
       <c r="W12" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -3040,10 +3304,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>15.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -3054,16 +3318,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>515580</t>
+          <t>006476</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>科技100ETF华泰柏瑞</t>
+          <t>南方原油C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.6485</v>
+        <v>1.6803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3079,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>58.84</v>
+        <v>53.93</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3098,37 +3362,37 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>100.03</v>
+        <v>65.06</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.4631</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>15.7</v>
+        <v>23.6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3136,10 +3400,10 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>2.876</v>
       </c>
       <c r="W13" t="n">
-        <v>92.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -3155,10 +3419,10 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>38.9</v>
+        <v>31.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>-2.5</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -3169,20 +3433,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>501060</t>
+          <t>118002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中金中证优选300指数(LOF)A</t>
+          <t>易方达标普消费品指数A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.4033</v>
+        <v>3.0291</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3194,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>54.36</v>
+        <v>56.19</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3213,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>104.36</v>
+        <v>51.65</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3225,25 +3489,25 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9129</v>
+        <v>0.7839</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>12</v>
+        <v>21.2</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3251,10 +3515,10 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.635</v>
+        <v>1.057</v>
       </c>
       <c r="W14" t="n">
-        <v>93.7</v>
+        <v>82.2</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -3270,10 +3534,10 @@
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>24.8</v>
+        <v>28.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -3284,111 +3548,111 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>050025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>消费ETF汇添富</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.9716</v>
+        <v>5.2811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>89.04000000000001</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.8005</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="S15" t="n">
         <v>-1</v>
       </c>
-      <c r="G15" t="n">
-        <v>42.47</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.2835</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
       <c r="T15" t="n">
-        <v>14.2</v>
+        <v>26.6</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.725</v>
+        <v>0.662</v>
       </c>
       <c r="W15" t="n">
-        <v>10</v>
+        <v>98.7</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>51.23</v>
+        <v>18.73</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3399,20 +3663,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>008115</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>沪深300ETF易方达</t>
+          <t>天弘中证红利低波动100联接C</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.4392</v>
+        <v>1.7742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3424,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>63.39</v>
+        <v>51.98</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -3443,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>108.01</v>
+        <v>113.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3462,50 +3726,510 @@
         <v>-1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9031</v>
+        <v>0.6455</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>10</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="W16" t="n">
+        <v>94</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>510580</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>中证500ETF易方达</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.6312</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>82.06</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="S16" t="n">
+      <c r="N17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8086</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
         <v>-1.5</v>
       </c>
-      <c r="T16" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="U16" t="inlineStr">
+      <c r="T17" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>震荡</t>
         </is>
       </c>
-      <c r="V16" t="n">
-        <v>0.766</v>
-      </c>
-      <c r="W16" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="V17" t="n">
+        <v>1.179</v>
+      </c>
+      <c r="W17" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA17" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>011555</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>海富通欣利混合C</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.4468</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.7917999999999999</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="W18" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>000369</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>广发全球医疗保健指数人民币(QDII)A</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2.5067</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="W19" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>510310</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>沪深300ETF易方达</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>62.28</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>89.73999999999999</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>19</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="W20" t="n">
+        <v>82</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
         <v>37.4</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB20" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>持有</t>
         </is>

--- a/fund.xlsx
+++ b/fund.xlsx
@@ -585,53 +585,53 @@
           <t>61.62</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>-2.08</v>
+      <c r="D3" t="n">
+        <v>-1.16</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.16</v>
+        <v>-3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3500000000000001</v>
+        <v>0.1299999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.01000000000000023</v>
+        <v>-0.03000000000000025</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.870000000000001</v>
+        <v>-6.219999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.479999999999999</v>
+        <v>-1.180000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>16.19</v>
+        <v>15.45</v>
       </c>
       <c r="K3" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>-3.76</v>
+        <v>21.75</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-1.5</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4.6</v>
+        <v>-5.789999999999999</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>7.56</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-15.49</v>
+        <v>-18.92</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-12.01</v>
+        <v>-11.07</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1499999999999986</v>
+        <v>-0.4600000000000009</v>
       </c>
       <c r="S3" t="n">
-        <v>19.77</v>
+        <v>19.38</v>
       </c>
       <c r="T3" t="n">
-        <v>0.52</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="4">
@@ -650,53 +650,53 @@
           <t>131.60</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>-2.45</v>
+      <c r="D4" t="n">
+        <v>-0.3699999999999999</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-4.33</v>
+        <v>-5.64</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6.16</v>
+        <v>5.56</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.05</v>
+        <v>-4.87</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-16.54</v>
+        <v>-15.55</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.869999999999999</v>
+        <v>-4.920000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>17.72</v>
+        <v>16.92</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>-4.13</v>
+        <v>45.9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.71</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-5.42</v>
+        <v>-8.43</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>10.41</v>
+        <v>12.99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-20.53</v>
+        <v>-23.76</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-21.68</v>
+        <v>-20.4</v>
       </c>
       <c r="R4" t="n">
-        <v>-3.539999999999999</v>
+        <v>-4.2</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>24.7</v>
+        <v>20.85</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>25.43</v>
       </c>
     </row>
     <row r="5">
@@ -716,52 +716,52 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-4.51</v>
+        <v>-3.15</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-4.54</v>
+        <v>-5.140000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>2.57</v>
+        <v>1.46</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-10.59</v>
+        <v>-10.07</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-23.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-13.94</v>
+        <v>-22.74</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-16.04</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.239999999999998</v>
+        <v>-2.08</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.23</v>
+        <v>-4.579999999999998</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-6.19</v>
+        <v>-3.49</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-5.63</v>
+        <v>-7.93</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>6.82</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-26.07</v>
+        <v>-28.96</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-28.54</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-12.61</v>
+        <v>-27.59</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>-15.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3400000000000016</v>
+        <v>1.85</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-24.76</v>
+        <v>-25.05</v>
       </c>
     </row>
     <row r="6">
@@ -780,53 +780,53 @@
           <t>101.98</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>1.53</v>
+      <c r="D6" t="n">
+        <v>0.8400000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7799999999999998</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-3.77</v>
+        <v>-0.2999999999999998</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-6.05</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>10.05</v>
+        <v>13.18</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>29.45</v>
+        <v>27.45</v>
       </c>
       <c r="I6" t="n">
-        <v>3.16</v>
+        <v>3.59</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.609999999999999</v>
+        <v>-7.26</v>
       </c>
       <c r="K6" t="n">
-        <v>19.77</v>
+        <v>19.5</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1500000000000004</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-1.87</v>
+        <v>0.5</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-3.089999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4800000000000004</v>
+        <v>1.380000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-5.429999999999998</v>
+        <v>-5.709999999999999</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>24.31</v>
+        <v>22.6</v>
       </c>
       <c r="R6" t="n">
-        <v>4.49</v>
+        <v>4.31</v>
       </c>
       <c r="S6" t="n">
-        <v>-4.029999999999999</v>
+        <v>-3.33</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7600000000000002</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="7">
@@ -846,25 +846,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>6.16</v>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.98</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>8.860000000000001</v>
+        <v>13.25</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>25.9</v>
+        <v>26.68</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-18.73</v>
+        <v>-17.81</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-23.95</v>
+        <v>-24.22</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -872,25 +872,25 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-0.27</v>
+        <v>-1.28</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-3.67</v>
+        <v>-6.089999999999999</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>10.41</v>
       </c>
-      <c r="P7" s="3" t="n">
-        <v>-6.619999999999997</v>
+      <c r="P7" t="n">
+        <v>-5.639999999999999</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>20.76</v>
+        <v>21.83</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-17.4</v>
+        <v>-17.09</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-20.37</v>
+        <v>-20.29</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -938,29 +938,29 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>-1.68</v>
+      <c r="M8" t="n">
+        <v>-0.3400000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.25</v>
+        <v>-2.789999999999999</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>7.430000000000001</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-15.48</v>
+        <v>-18.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.140000000000001</v>
+        <v>-4.849999999999998</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0.7200000000000006</v>
       </c>
       <c r="S8" t="n">
-        <v>3.58</v>
+        <v>3.93</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-20.53</v>
+        <v>-20.47</v>
       </c>
     </row>
     <row r="9">
@@ -979,29 +979,29 @@
           <t>2637.86</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>1.68</v>
+      <c r="D9" t="n">
+        <v>0.3400000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-4.25</v>
+        <v>2.789999999999999</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-7.430000000000001</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>15.48</v>
+        <v>18.89</v>
       </c>
       <c r="H9" t="n">
-        <v>5.140000000000001</v>
+        <v>4.849999999999998</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.33</v>
+        <v>-0.7200000000000006</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.58</v>
+        <v>-3.93</v>
       </c>
       <c r="K9" t="n">
-        <v>20.53</v>
+        <v>20.47</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1044,53 +1044,53 @@
           <t>380.36</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>-0.06999999999999984</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>4.960000000000001</v>
+      <c r="D10" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.800000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.87</v>
+        <v>-1.82</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.27</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>13.08</v>
+        <v>-1.78</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.269999999999996</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.829999999999999</v>
+        <v>-7.240000000000001</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43.91</v>
+        <v>45.88</v>
       </c>
       <c r="K10" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.3799999999999999</v>
+        <v>13.98</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.9899999999999984</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>5.61</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-19.75</v>
+        <v>-20.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.939999999999998</v>
+        <v>3.419999999999998</v>
       </c>
       <c r="R10" t="n">
-        <v>-6.499999999999999</v>
+        <v>-6.52</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>47.49</v>
+        <v>49.81</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.92</v>
+        <v>-6.49</v>
       </c>
     </row>
     <row r="11">
@@ -1110,52 +1110,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>3.72</v>
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.1100000000000003</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.22</v>
+        <v>-0.9500000000000002</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.47</v>
+        <v>-0.6900000000000002</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>-0.7199999999999989</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.709999999999999</v>
+        <v>-4.830000000000001</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>31.91</v>
+        <v>33.53</v>
       </c>
       <c r="K11" t="n">
-        <v>20.84</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>-2.83</v>
+        <v>21.24</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.23</v>
       </c>
       <c r="N11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.03</v>
+        <v>-2.899999999999999</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>6.48</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-17.95</v>
+        <v>-19.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.890000000000001</v>
+        <v>-5.569999999999997</v>
       </c>
       <c r="R11" t="n">
-        <v>-4.379999999999999</v>
+        <v>-4.11</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>35.49</v>
+        <v>37.46</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="12">
@@ -1174,26 +1174,26 @@
           <t>509.35</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>-1.45</v>
+      <c r="D12" s="3" t="n">
+        <v>-5.41</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.14</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-13.41</v>
+        <v>-13.42</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-7.710000000000001</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-7.050000000000001</v>
+        <v>-6.949999999999999</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>-10.16</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.01000000000001</v>
+        <v>34.62</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.66</v>
+        <v>-0.1899999999999995</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>-3.13</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>-3.23</v>
+        <v>-5.75</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-2.829999999999999</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>-9.16</v>
+        <v>-5.99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>-23.19</v>
+        <v>-25.84</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>-12.19</v>
+        <v>-15.01</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>37.34</v>
+        <v>35.34</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.08000000000000007</v>
+        <v>3.74</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1244,52 +1244,52 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.4399999999999999</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-4.909999999999999</v>
+        <v>-2.54</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-2.420000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-15.63</v>
+        <v>-16.87</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.32</v>
+        <v>-10.49</v>
       </c>
       <c r="J13" t="n">
-        <v>13.59</v>
+        <v>14.84</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>35.02</v>
+        <v>36.23999999999999</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-5.98</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-0.6500000000000004</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-0.6599999999999993</v>
+        <v>-2.88</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>-7.489999999999999</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>5.01</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-12.89</v>
+        <v>-15.65</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-20.77</v>
+        <v>-21.72</v>
       </c>
       <c r="R13" t="n">
-        <v>-8.989999999999998</v>
+        <v>-9.77</v>
       </c>
       <c r="S13" t="n">
-        <v>17.17</v>
+        <v>18.77</v>
       </c>
       <c r="T13" t="n">
-        <v>14.49</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="14">
@@ -1309,52 +1309,52 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>4.92</v>
+        <v>-1.67</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.5999999999999996</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-9.100000000000001</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>-8.040000000000001</v>
+        <v>-7.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-5.44</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3399999999999999</v>
+        <v>-4.240000000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>-14.91</v>
+        <v>-13.64</v>
       </c>
       <c r="J14" t="n">
-        <v>2.410000000000001</v>
+        <v>3.22</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>27.51</v>
+        <v>26.86</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>-3.81</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>-4.850000000000001</v>
+        <v>-2.01</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>-3.389999999999999</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.3900000000000006</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-23.52</v>
+        <v>-24.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.800000000000001</v>
+        <v>-9.09</v>
       </c>
       <c r="R14" t="n">
-        <v>-13.58</v>
+        <v>-12.92</v>
       </c>
       <c r="S14" t="n">
-        <v>5.990000000000001</v>
+        <v>7.149999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>6.979999999999999</v>
+        <v>6.389999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1374,25 +1374,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.3000000000000003</v>
+        <v>-0.07999999999999985</v>
       </c>
       <c r="E15" t="n">
-        <v>1.73</v>
+        <v>-1.84</v>
       </c>
       <c r="F15" t="n">
-        <v>2.09</v>
+        <v>4.149999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1499999999999999</v>
+        <v>2.05</v>
       </c>
       <c r="H15" t="n">
-        <v>4.41</v>
+        <v>2.82</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5699999999999985</v>
+        <v>-1.530000000000001</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22.14</v>
+        <v>23.58</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1400,25 +1400,25 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.6399999999999997</v>
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>-4.629999999999999</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>6.34</v>
+        <v>11.58</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-15.33</v>
+        <v>-16.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.7300000000000004</v>
+        <v>-2.029999999999998</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7600000000000016</v>
+        <v>-0.8100000000000005</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>25.72</v>
+        <v>27.51</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1442,53 +1442,53 @@
           <t>380.36</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>-0.3399999999999999</v>
+      <c r="D16" s="3" t="n">
+        <v>-2.11</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5.960000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="F16" t="n">
-        <v>1.19</v>
+        <v>0.4100000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7000000000000002</v>
+        <v>1.69</v>
       </c>
       <c r="H16" t="n">
-        <v>8.149999999999999</v>
+        <v>4.640000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-10.41</v>
+        <v>-11.25</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>28.42</v>
+        <v>30.08</v>
       </c>
       <c r="K16" t="n">
-        <v>2.470000000000001</v>
+        <v>3.69</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-2.02</v>
+        <v>-2.45</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>4.87</v>
+        <v>5.470000000000001</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>5.44</v>
+        <v>7.840000000000001</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-16.18</v>
+        <v>-17.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.009999999999998</v>
+        <v>-0.2099999999999973</v>
       </c>
       <c r="R16" t="n">
-        <v>-9.08</v>
+        <v>-10.53</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>32</v>
+        <v>34.01</v>
       </c>
       <c r="T16" t="n">
-        <v>-18.06</v>
+        <v>-16.78</v>
       </c>
     </row>
     <row r="17">
@@ -1508,52 +1508,52 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-3.17</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0.7199999999999998</v>
+        <v>-3.09</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>6.710000000000001</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-10.34</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>10.62</v>
+        <v>15.03</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.859999999999999</v>
+        <v>-5.060000000000002</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>34.91</v>
+        <v>31.11</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>34.56</v>
+        <v>32.42</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>33.69</v>
+        <v>34.39</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-4.85</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-2.34</v>
+        <v>-3.43</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>3.920000000000002</v>
       </c>
       <c r="O17" t="n">
-        <v>3.53</v>
+        <v>-2.909999999999998</v>
       </c>
       <c r="P17" t="n">
-        <v>-4.859999999999998</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>-14</v>
+        <v>-3.859999999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-9.91</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>36.24</v>
+        <v>31.83</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>38.14</v>
+        <v>36.35</v>
       </c>
       <c r="T17" t="n">
-        <v>13.16</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="18">
@@ -1572,53 +1572,53 @@
           <t>294.30</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>-0.9299999999999997</v>
+      <c r="D18" s="2" t="n">
+        <v>2.52</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-7.85</v>
+        <v>-12.79</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>59.56</v>
+        <v>63.45</v>
       </c>
       <c r="G18" t="n">
-        <v>0.21</v>
+        <v>-1.85</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>-28.06</v>
+        <v>-26.44</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-23.88</v>
+        <v>-23.73</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>26.19</v>
+        <v>25.56</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>71.56</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>-2.61</v>
+        <v>72.08</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>2.18</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>-8.940000000000001</v>
+        <v>-15.58</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>63.81</v>
+        <v>70.88</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>-15.27</v>
+        <v>-20.74</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>-33.2</v>
+        <v>-31.29</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>-22.55</v>
+        <v>-23.01</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>29.77</v>
+        <v>29.49</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>51.03</v>
+        <v>51.61</v>
       </c>
     </row>
     <row r="22">
@@ -1767,26 +1767,26 @@
           <t>146.66</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-0.1</v>
+      <c r="D24" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1.86</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-1.4</v>
+        <v>-3.39</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4.56</v>
+        <v>4.8</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>13.07</v>
+        <v>13.2</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>9.73</v>
+        <v>10.77</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-6.9</v>
+        <v>-7.71</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1794,25 +1794,25 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.11</v>
+        <v>1.53</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-0.89</v>
+        <v>-2.49</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>3.88</v>
+        <v>4.18</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>10.26</v>
+        <v>10.35</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>12.4</v>
+        <v>13.16</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3900000000000001</v>
+        <v>-0.1599999999999999</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -1860,29 +1860,29 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="M25" t="n">
-        <v>0.03999999999999998</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>0.21</v>
+      <c r="M25" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>-0.33</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-0.6799999999999999</v>
+        <v>-0.62</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-2.81</v>
+        <v>-2.85</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>2.67</v>
+        <v>2.390000000000001</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>7.29</v>
+        <v>7.550000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
     </row>
   </sheetData>
@@ -2053,20 +2053,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>050025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>消费ETF汇添富</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.9554</v>
+        <v>5.3166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>40.52</v>
+        <v>67</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2097,67 +2097,67 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-4.43</v>
+        <v>95.12</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>28</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="W2" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="W2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.5</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -2168,20 +2168,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>501060</t>
+          <t>159928</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中金中证优选300指数(LOF)A</t>
+          <t>消费ETF汇添富</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.3946</v>
+        <v>2.9512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>52.03</v>
+        <v>39.64</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>90.73999999999999</v>
+        <v>-8.67</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -2224,25 +2224,25 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7603</v>
+        <v>0.1286</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.626</v>
       </c>
       <c r="W3" t="n">
-        <v>93.09999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>24.8</v>
+        <v>51.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -2283,20 +2283,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>040046</t>
+          <t>515580</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>华安纳斯达克100ETF联接(QDII)A</t>
+          <t>科技100ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.6176</v>
+        <v>2.6533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2308,15 +2308,15 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>72.73999999999999</v>
+        <v>57.25</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>100.2</v>
+        <v>63.76</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2339,39 +2339,39 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8994</v>
+        <v>0.7729</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>27.3</v>
+        <v>16.7</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.959</v>
+        <v>1.157</v>
       </c>
       <c r="W4" t="n">
-        <v>99.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>31.24</v>
+        <v>38.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -2398,20 +2398,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>513880</t>
+          <t>012832</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>日经225ETF华安</t>
+          <t>南方中证新能源ETF联接C</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.8636</v>
+        <v>0.7559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2423,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>63.38</v>
+        <v>60.17</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>92.52</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -2461,18 +2461,18 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8446</v>
+        <v>0.7922</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>18.9</v>
+        <v>15.7</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2480,13 +2480,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.487</v>
+        <v>1.273</v>
       </c>
       <c r="W5" t="n">
-        <v>98.09999999999999</v>
+        <v>51.6</v>
       </c>
       <c r="X5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>27.43</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>000216</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>交银优选回报灵活配置混合C</t>
+          <t>华安黄金ETF联接A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.5492</v>
+        <v>3.5841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>63.1</v>
+        <v>44.36</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2557,37 +2557,37 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>84.84999999999999</v>
+        <v>-17.19</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8056</v>
+        <v>0.4084</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>21.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -2595,29 +2595,29 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.079</v>
+        <v>1.202</v>
       </c>
       <c r="W6" t="n">
-        <v>99.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="X6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
       <c r="AA6" t="n">
-        <v>3.91</v>
+        <v>25.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>-2.5</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -2628,20 +2628,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>012832</t>
+          <t>510310</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南方中证新能源ETF联接C</t>
+          <t>沪深300ETF易方达</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7446</v>
+        <v>2.444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>56.31</v>
+        <v>62.13</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>73.67</v>
+        <v>80.34</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.712</v>
+        <v>0.79</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>15.2</v>
+        <v>19.6</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.335</v>
+        <v>0.704</v>
       </c>
       <c r="W7" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>65.01000000000001</v>
+        <v>36.33</v>
       </c>
       <c r="AB7" t="n">
         <v>-1</v>
@@ -2743,16 +2743,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>515580</t>
+          <t>159687</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>科技100ETF华泰柏瑞</t>
+          <t>亚太精选ETF南方</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.6622</v>
+        <v>1.7052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>58.56</v>
+        <v>57.39</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>84.44</v>
+        <v>75.47</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2806,18 +2806,18 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8331</v>
+        <v>0.7377</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.214</v>
+        <v>1.362</v>
       </c>
       <c r="W8" t="n">
-        <v>92.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>38.9</v>
+        <v>15.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -2858,20 +2858,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>000216</t>
+          <t>011555</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>华安黄金ETF联接A</t>
+          <t>海富通欣利混合C</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.5941</v>
+        <v>1.447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2883,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>45.14</v>
+        <v>55.32</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.93</v>
+        <v>63.06</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4856</v>
+        <v>0.7622</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>9.199999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2940,17 +2940,17 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1.268</v>
+        <v>0.312</v>
       </c>
       <c r="W9" t="n">
-        <v>77.2</v>
+        <v>95.2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>25.07</v>
+        <v>12.06</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -2973,40 +2973,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>008115</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
+          <t>天弘中证红利低波动100联接C</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.779</v>
+        <v>1.772</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>87.56</v>
+        <v>50.73</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3017,15 +3017,15 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>98.36</v>
+        <v>98.66</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -3036,48 +3036,48 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.6054</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>58.5</v>
+        <v>9.6</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.046</v>
+        <v>0.466</v>
       </c>
       <c r="W10" t="n">
-        <v>99.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="X10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>1.88</v>
+        <v>13.26</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -3088,20 +3088,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>012805</t>
+          <t>006476</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>广发恒生科技ETF联接(QDII)C</t>
+          <t>南方原油C</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7852</v>
+        <v>1.7087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3113,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>44.97</v>
+        <v>55.92</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>21.09</v>
+        <v>101.44</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4932</v>
+        <v>0.5722</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>16.6</v>
+        <v>22.8</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -3170,29 +3170,29 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1.468</v>
+        <v>2.745</v>
       </c>
       <c r="W11" t="n">
-        <v>46.6</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>53.89</v>
+        <v>31.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -3203,20 +3203,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>159687</t>
+          <t>513880</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>亚太精选ETF南方</t>
+          <t>日经225ETF华安</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.7274</v>
+        <v>1.8514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3228,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>61.42</v>
+        <v>61.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -3247,15 +3247,15 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>99.25</v>
+        <v>85.41</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -3266,18 +3266,18 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.7781</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -3285,13 +3285,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1.457</v>
+        <v>1.437</v>
       </c>
       <c r="W12" t="n">
-        <v>94.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>15.3</v>
+        <v>27.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -3318,20 +3318,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>006476</t>
+          <t>501060</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>南方原油C</t>
+          <t>中金中证优选300指数(LOF)A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.6803</v>
+        <v>2.3914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>53.93</v>
+        <v>51.01</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3362,15 +3362,15 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>65.06</v>
+        <v>54.38</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4631</v>
+        <v>0.7014</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>23.6</v>
+        <v>10.6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3400,29 +3400,29 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>2.876</v>
+        <v>0.535</v>
       </c>
       <c r="W13" t="n">
-        <v>92</v>
+        <v>92.8</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>31.68</v>
+        <v>24.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -3433,20 +3433,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>040046</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>易方达标普消费品指数A</t>
+          <t>华安纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.0291</v>
+        <v>7.5428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>56.19</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3477,15 +3477,15 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>51.65</v>
+        <v>91.19</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.7839</v>
+        <v>0.7748</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -3507,37 +3507,37 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>21.2</v>
+        <v>28.6</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1.057</v>
+        <v>0.916</v>
       </c>
       <c r="W14" t="n">
-        <v>82.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>28.4</v>
+        <v>31.24</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -3548,20 +3548,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>050025</t>
+          <t>118002</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>易方达标普消费品指数A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.2811</v>
+        <v>2.9556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>66.18000000000001</v>
+        <v>48.11</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>89.04000000000001</v>
+        <v>-25.76</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3604,52 +3604,52 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8005</v>
+        <v>0.5478</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>26.6</v>
+        <v>18.1</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.662</v>
+        <v>1.069</v>
       </c>
       <c r="W15" t="n">
-        <v>98.7</v>
+        <v>78.5</v>
       </c>
       <c r="X15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>18.73</v>
+        <v>28.4</v>
       </c>
       <c r="AB15" t="n">
         <v>1</v>
@@ -3663,20 +3663,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>008115</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>天弘中证红利低波动100联接C</t>
+          <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.7742</v>
+        <v>1.7767</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3688,15 +3688,15 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>51.98</v>
+        <v>72.27</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>113.2</v>
+        <v>75.38</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3719,40 +3719,40 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.7745</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="W16" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="X16" t="n">
         <v>-1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0.6455</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>10</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="W16" t="n">
-        <v>94</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
           <t>多头</t>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>13.26</v>
+        <v>1.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -3778,20 +3778,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>510580</t>
+          <t>000369</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中证500ETF易方达</t>
+          <t>广发全球医疗保健指数人民币(QDII)A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.6312</v>
+        <v>2.4878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>58.59</v>
+        <v>40.52</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3822,37 +3822,37 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>82.06</v>
+        <v>-19.52</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8086</v>
+        <v>0.1895</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="T17" t="n">
-        <v>17.7</v>
+        <v>16.1</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3860,29 +3860,29 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1.179</v>
+        <v>0.654</v>
       </c>
       <c r="W17" t="n">
-        <v>91.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>38.31</v>
+        <v>14.51</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -3893,20 +3893,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>011555</t>
+          <t>012805</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>海富通欣利混合C</t>
+          <t>广发恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.4468</v>
+        <v>0.7929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3918,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>55.29</v>
+        <v>47.55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3937,15 +3937,15 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>79.7</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>14.4</v>
+        <v>15.7</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3975,29 +3975,29 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.336</v>
+        <v>1.385</v>
       </c>
       <c r="W18" t="n">
-        <v>95.2</v>
+        <v>47.9</v>
       </c>
       <c r="X18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>12.06</v>
+        <v>53.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -4008,20 +4008,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>000369</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>广发全球医疗保健指数人民币(QDII)A</t>
+          <t>交银优选回报灵活配置混合C</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.5067</v>
+        <v>1.549</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>44.51</v>
+        <v>62.18</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>4.83</v>
+        <v>64.88</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3894</v>
+        <v>0.7635</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>15.5</v>
+        <v>21.9</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4090,26 +4090,26 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.705</v>
+        <v>0.074</v>
       </c>
       <c r="W19" t="n">
-        <v>83.09999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>14.51</v>
+        <v>3.91</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -4123,20 +4123,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>沪深300ETF易方达</t>
+          <t>中证500ETF易方达</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.444</v>
+        <v>1.6297</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>62.28</v>
+        <v>58.13</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -4167,15 +4167,15 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>89.73999999999999</v>
+        <v>67.42</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -4186,18 +4186,18 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.826</v>
+        <v>0.7692</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>19</v>
+        <v>17.8</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.756</v>
+        <v>1.105</v>
       </c>
       <c r="W20" t="n">
-        <v>82</v>
+        <v>91.5</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>37.4</v>
+        <v>38.31</v>
       </c>
       <c r="AB20" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>

--- a/fund.xlsx
+++ b/fund.xlsx
@@ -586,52 +586,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-3</v>
+        <v>-0.29</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>-5.18</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1299999999999999</v>
+        <v>0.9299999999999997</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.03000000000000025</v>
+        <v>0.6199999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.219999999999999</v>
+        <v>-6.800000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.180000000000001</v>
+        <v>0.08999999999999986</v>
       </c>
       <c r="J3" t="n">
-        <v>15.45</v>
+        <v>13.48</v>
       </c>
       <c r="K3" t="n">
-        <v>21.75</v>
+        <v>23.06</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-5.789999999999999</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>7.56</v>
+        <v>-6.549999999999999</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.550000000000001</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-18.92</v>
+        <v>-12.72</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-11.07</v>
+        <v>-13.74</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.4600000000000009</v>
+        <v>2.08</v>
       </c>
       <c r="S3" t="n">
-        <v>19.38</v>
+        <v>16.07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.28</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="4">
@@ -651,52 +651,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.3699999999999999</v>
+        <v>-0.85</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-5.64</v>
+        <v>-7.74</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5.56</v>
+        <v>6.05</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.87</v>
+        <v>-1.86</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-15.55</v>
+        <v>-17.75</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.920000000000001</v>
+        <v>-2.74</v>
       </c>
       <c r="J4" t="n">
-        <v>16.92</v>
+        <v>12.67</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>45.9</v>
+        <v>50.92</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.71</v>
+        <v>-1.16</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-8.43</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>12.99</v>
+        <v>9.670000000000002</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-23.76</v>
+        <v>-15.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-20.4</v>
+        <v>-24.69</v>
       </c>
       <c r="R4" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>20.85</v>
+        <v>-0.75</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15.26</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>25.43</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="5">
@@ -715,53 +715,53 @@
           <t>553.76</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>-3.15</v>
+      <c r="D5" t="n">
+        <v>0.74</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-5.140000000000001</v>
+        <v>-8.59</v>
       </c>
       <c r="F5" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-10.07</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-22.74</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-16.04</v>
+        <v>-24.28</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-14.66</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.08</v>
+        <v>-3.91</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.579999999999998</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>-3.49</v>
+        <v>-4.449999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4299999999999999</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>-9.959999999999999</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.680000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-28.96</v>
+        <v>-21.45</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-27.59</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>-15.32</v>
+        <v>-31.22</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-12.67</v>
       </c>
       <c r="S5" t="n">
-        <v>1.85</v>
+        <v>-1.32</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-25.05</v>
+        <v>-24.68</v>
       </c>
     </row>
     <row r="6">
@@ -781,52 +781,52 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2999999999999998</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-6.05</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>13.18</v>
+        <v>0.6199999999999992</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.54</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>27.45</v>
+        <v>29.85</v>
       </c>
       <c r="I6" t="n">
-        <v>3.59</v>
+        <v>3.43</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.26</v>
+        <v>-4.44</v>
       </c>
       <c r="K6" t="n">
-        <v>19.5</v>
+        <v>15.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-3.089999999999999</v>
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.380000000000001</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-5.709999999999999</v>
+        <v>1.910000000000001</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-8.800000000000001</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>22.6</v>
+        <v>22.91</v>
       </c>
       <c r="R6" t="n">
-        <v>4.31</v>
+        <v>5.42</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.33</v>
+        <v>-1.85</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.97</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="7">
@@ -845,52 +845,52 @@
           <t>132.24</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>13.25</v>
+      <c r="D7" s="2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.4100000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>26.68</v>
+        <v>37.59999999999999</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-17.81</v>
+        <v>-17.85</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-24.22</v>
+        <v>-23.93</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-6.089999999999999</v>
+      <c r="M7" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-2.669999999999999</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-5.639999999999999</v>
+        <v>9.710000000000001</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>-13.75</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>21.83</v>
+        <v>30.66</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-17.09</v>
+        <v>-15.86</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-20.29</v>
+        <v>-21.34</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -939,28 +939,28 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3400000000000001</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.789999999999999</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>7.430000000000001</v>
+        <v>-1.369999999999999</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.620000000000001</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-18.89</v>
+        <v>-13.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.849999999999998</v>
+        <v>-6.940000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7200000000000006</v>
+        <v>1.99</v>
       </c>
       <c r="S8" t="n">
-        <v>3.93</v>
+        <v>2.59</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-20.47</v>
+        <v>-20.23</v>
       </c>
     </row>
     <row r="9">
@@ -980,28 +980,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3400000000000001</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>2.789999999999999</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-7.430000000000001</v>
+        <v>1.369999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-3.620000000000001</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>18.89</v>
+        <v>13.34</v>
       </c>
       <c r="H9" t="n">
-        <v>4.849999999999998</v>
+        <v>6.940000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7200000000000006</v>
+        <v>-1.99</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.93</v>
+        <v>-2.59</v>
       </c>
       <c r="K9" t="n">
-        <v>20.47</v>
+        <v>20.23</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1044,53 +1044,53 @@
           <t>380.36</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.800000000000001</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-1.82</v>
+      <c r="D10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>-6.1</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.78</v>
+        <v>-4.47</v>
       </c>
       <c r="H10" t="n">
-        <v>8.269999999999996</v>
+        <v>4.52</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.240000000000001</v>
+        <v>-0.4799999999999995</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>45.88</v>
+        <v>44.27</v>
       </c>
       <c r="K10" t="n">
-        <v>13.98</v>
+        <v>16.93</v>
       </c>
       <c r="M10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.9899999999999984</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>5.61</v>
+        <v>0.12</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>6.470000000000001</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-2.479999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-20.67</v>
+        <v>-17.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.419999999999998</v>
+        <v>-2.420000000000002</v>
       </c>
       <c r="R10" t="n">
-        <v>-6.52</v>
+        <v>1.510000000000001</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>49.81</v>
+        <v>46.86</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.49</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="11">
@@ -1110,52 +1110,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5700000000000001</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.1100000000000003</v>
+        <v>-0.51</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>3.109999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9500000000000002</v>
+        <v>-3.470000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6900000000000002</v>
+        <v>-2.05</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7199999999999989</v>
+        <v>-4.98</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.830000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>33.53</v>
+        <v>31.55</v>
       </c>
       <c r="K11" t="n">
-        <v>21.24</v>
+        <v>22.64</v>
       </c>
       <c r="M11" t="n">
-        <v>0.23</v>
+        <v>-0.8200000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.899999999999999</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>6.48</v>
+        <v>1.74</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1500000000000004</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-5.569999999999997</v>
+        <v>-15.39</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-11.92</v>
       </c>
       <c r="R11" t="n">
-        <v>-4.11</v>
+        <v>3.67</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>37.46</v>
+        <v>34.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0.77</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="12">
@@ -1174,52 +1174,52 @@
           <t>509.35</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>-5.41</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.04000000000000004</v>
+      <c r="D12" t="n">
+        <v>-0.4399999999999999</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-3.87</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-13.42</v>
+        <v>-13.56</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-6.949999999999999</v>
+        <v>-7.12</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-10.16</v>
+        <v>-13.12</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>34.62</v>
+        <v>28.9</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1899999999999995</v>
+        <v>4.86</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M12" s="3" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-2.829999999999999</v>
+      <c r="M12" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>-5.239999999999999</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>-5.99</v>
+        <v>-9.939999999999998</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>-25.84</v>
+        <v>-20.46</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>-15.01</v>
+        <v>-20.06</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>35.34</v>
+        <v>30.89</v>
       </c>
       <c r="S12" t="n">
-        <v>3.74</v>
+        <v>7.45</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1244,52 +1244,52 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-2.54</v>
+        <v>-3.24</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-4.7</v>
+        <v>-6.720000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.420000000000001</v>
+        <v>-1.16</v>
       </c>
       <c r="G13" t="n">
-        <v>3.24</v>
+        <v>3.88</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-16.87</v>
+        <v>-23.3</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.49</v>
+        <v>-4.93</v>
       </c>
       <c r="J13" t="n">
-        <v>14.84</v>
+        <v>13.06</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>36.23999999999999</v>
+        <v>37.93</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-2.88</v>
+        <v>-3.55</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-7.489999999999999</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>5.01</v>
+        <v>-8.09</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.460000000000001</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-15.65</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-21.72</v>
+        <v>-30.24</v>
       </c>
       <c r="R13" t="n">
-        <v>-9.77</v>
+        <v>-2.94</v>
       </c>
       <c r="S13" t="n">
-        <v>18.77</v>
+        <v>15.65</v>
       </c>
       <c r="T13" t="n">
-        <v>15.77</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="14">
@@ -1309,52 +1309,52 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-1.67</v>
+        <v>-3.8</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5999999999999996</v>
+        <v>-1.63</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-7.04</v>
+        <v>-7.31</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.44</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-4.240000000000002</v>
+        <v>-4.08</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>-11.38</v>
       </c>
       <c r="I14" t="n">
-        <v>-13.64</v>
+        <v>-8.58</v>
       </c>
       <c r="J14" t="n">
-        <v>3.22</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>26.86</v>
+        <v>25.51</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>-3.389999999999999</v>
+        <v>-4.11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-2.999999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3900000000000006</v>
+        <v>-3.69</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-24.33</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-9.09</v>
+        <v>-17.42</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>-18.32</v>
       </c>
       <c r="R14" t="n">
-        <v>-12.92</v>
+        <v>-6.59</v>
       </c>
       <c r="S14" t="n">
-        <v>7.149999999999999</v>
+        <v>6.19</v>
       </c>
       <c r="T14" t="n">
-        <v>6.389999999999999</v>
+        <v>5.279999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1374,25 +1374,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07999999999999985</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.84</v>
+        <v>0.5199999999999996</v>
       </c>
       <c r="F15" t="n">
-        <v>4.149999999999999</v>
+        <v>-0.9900000000000002</v>
       </c>
       <c r="G15" t="n">
-        <v>2.05</v>
+        <v>4.989999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.82</v>
+        <v>-1.25</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.530000000000001</v>
+        <v>2.58</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>23.58</v>
+        <v>23.76</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1400,25 +1400,25 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-0.4199999999999999</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>-4.629999999999999</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>11.58</v>
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.8499999999999996</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.630000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-16.84</v>
+        <v>-8.350000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.029999999999998</v>
+        <v>-8.190000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.8100000000000005</v>
+        <v>4.57</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>27.51</v>
+        <v>26.35</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1442,53 +1442,53 @@
           <t>380.36</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>-2.11</v>
+      <c r="D16" t="n">
+        <v>-0.73</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>8.26</v>
+        <v>7.390000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4100000000000001</v>
+        <v>-2.800000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1.69</v>
+        <v>-1.52</v>
       </c>
       <c r="H16" t="n">
-        <v>4.640000000000001</v>
+        <v>7.080000000000002</v>
       </c>
       <c r="I16" t="n">
-        <v>-11.25</v>
+        <v>-5.02</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>30.08</v>
+        <v>25.68</v>
       </c>
       <c r="K16" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>-2.45</v>
+        <v>6.859999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1.04</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>5.470000000000001</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>7.840000000000001</v>
+        <v>6.020000000000001</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.8200000000000003</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-17.2</v>
+        <v>-14.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2099999999999973</v>
+        <v>0.1400000000000006</v>
       </c>
       <c r="R16" t="n">
-        <v>-10.53</v>
+        <v>-3.029999999999999</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>34.01</v>
+        <v>28.27</v>
       </c>
       <c r="T16" t="n">
-        <v>-16.78</v>
+        <v>-13.37</v>
       </c>
     </row>
     <row r="17">
@@ -1508,52 +1508,52 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-3.09</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>6.710000000000001</v>
+        <v>-2.86</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-5.86</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-10.34</v>
+        <v>-7.140000000000001</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>15.03</v>
+        <v>24.22</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.060000000000002</v>
+        <v>-7.970000000000002</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>31.11</v>
+        <v>32.86</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>32.42</v>
+        <v>30.01</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>34.39</v>
+        <v>35.92</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-3.43</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>3.920000000000002</v>
+        <v>-3.17</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>-7.23</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.909999999999998</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-3.859999999999999</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-9.91</v>
+        <v>-3.52</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>-14.91</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>31.83</v>
+        <v>34.84999999999999</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>36.35</v>
+        <v>32.6</v>
       </c>
       <c r="T17" t="n">
-        <v>13.92</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="18">
@@ -1573,52 +1573,52 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2.52</v>
+        <v>11.58</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-12.79</v>
+        <v>-9.370000000000001</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>63.45</v>
+        <v>51.44</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.85</v>
+        <v>4.56</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>-26.44</v>
+        <v>-24.5</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-23.73</v>
+        <v>-23</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>25.56</v>
+        <v>26.02</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>72.08</v>
+        <v>64.31</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2.18</v>
+        <v>11.27</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>-15.58</v>
+        <v>-10.74</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>70.88</v>
+        <v>55.06</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>-20.74</v>
+        <v>-8.780000000000001</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>-31.29</v>
+        <v>-31.44</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>-23.01</v>
+        <v>-21.01</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>29.49</v>
+        <v>28.61</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>51.61</v>
+        <v>44.08000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1767,26 +1767,26 @@
           <t>146.66</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0.02000000000000002</v>
+      <c r="D24" s="2" t="n">
+        <v>0.32</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.86</v>
+        <v>1.38</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-3.39</v>
+        <v>-2.81</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4.8</v>
+        <v>4.739999999999999</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>13.2</v>
+        <v>13.54</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10.77</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-7.71</v>
+        <v>-5.83</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1794,25 +1794,25 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-2.49</v>
+        <v>-1.96</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>4.18</v>
+        <v>4.029999999999999</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>10.35</v>
+        <v>10.54</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>13.16</v>
+        <v>11.24</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1599999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -1860,29 +1860,29 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="2" t="n">
-        <v>0.15</v>
+      <c r="M25" s="3" t="n">
+        <v>-0.18</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.1599999999999999</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.71</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-2.85</v>
+        <v>-3</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>2.390000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>7.550000000000001</v>
+        <v>6.84</v>
       </c>
       <c r="T25" t="n">
-        <v>3.76</v>
+        <v>4.180000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2053,20 +2053,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>050025</t>
+          <t>118002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>易方达标普消费品指数A</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.3166</v>
+        <v>2.874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>67</v>
+        <v>39.82</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2097,67 +2097,67 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>95.12</v>
+        <v>-16.54</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.779</v>
+        <v>0.1962</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>28</v>
+        <v>17.9</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>0.655</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>99.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>18.73</v>
+        <v>28.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -2168,20 +2168,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>510310</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>消费ETF汇添富</t>
+          <t>沪深300ETF易方达</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.9512</v>
+        <v>2.4635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>39.64</v>
+        <v>64.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2212,67 +2212,67 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-8.67</v>
+        <v>89.53</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.7654</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="W3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.1286</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>0.626</v>
-      </c>
-      <c r="W3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="AA3" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -2283,20 +2283,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>515580</t>
+          <t>050025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技100ETF华泰柏瑞</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.6533</v>
+        <v>5.3346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>57.25</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>63.76</v>
+        <v>86.52</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7729</v>
+        <v>0.7137</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2357,21 +2357,21 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>16.7</v>
+        <v>29.8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>1.157</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>92.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>38.9</v>
+        <v>18.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -2398,20 +2398,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>012832</t>
+          <t>040046</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南方中证新能源ETF联接C</t>
+          <t>华安纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7559</v>
+        <v>7.7762</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2423,15 +2423,15 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>60.17</v>
+        <v>71.91</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>89.09999999999999</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -2461,32 +2461,32 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7922</v>
+        <v>0.8249</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T5" t="n">
-        <v>15.7</v>
+        <v>32.6</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.273</v>
+        <v>0.917</v>
       </c>
       <c r="W5" t="n">
-        <v>51.6</v>
+        <v>100</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>65.01000000000001</v>
+        <v>31.24</v>
       </c>
       <c r="AB5" t="n">
         <v>1</v>
@@ -2513,20 +2513,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>000216</t>
+          <t>011555</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>华安黄金ETF联接A</t>
+          <t>海富通欣利混合C</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.5841</v>
+        <v>1.4531</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>44.36</v>
+        <v>58.98</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-17.19</v>
+        <v>73.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2569,14 +2569,14 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4084</v>
+        <v>0.7877</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>9.300000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -2595,17 +2595,17 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.202</v>
+        <v>0.286</v>
       </c>
       <c r="W6" t="n">
-        <v>76.8</v>
+        <v>96.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>25.07</v>
+        <v>12.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -2628,32 +2628,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>012805</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>沪深300ETF易方达</t>
+          <t>广发恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.444</v>
+        <v>0.7874</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G7" t="n">
-        <v>62.13</v>
+        <v>46.5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2672,15 +2672,15 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>80.34</v>
+        <v>6.67</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.79</v>
+        <v>0.453</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>19.6</v>
+        <v>13.2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2710,26 +2710,26 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.704</v>
+        <v>1.369</v>
       </c>
       <c r="W7" t="n">
-        <v>82</v>
+        <v>46.9</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>36.33</v>
+        <v>53.89</v>
       </c>
       <c r="AB7" t="n">
         <v>-1</v>
@@ -2752,11 +2752,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.7052</v>
+        <v>1.7286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>57.39</v>
+        <v>60.05</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2787,51 +2787,51 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>75.47</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W8" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="X8" t="n">
         <v>-1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.7377</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>1.362</v>
-      </c>
-      <c r="W8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>15.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -2858,20 +2858,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>011555</t>
+          <t>006476</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>海富通欣利混合C</t>
+          <t>南方原油C</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.447</v>
+        <v>1.9146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2883,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>55.32</v>
+        <v>68.78</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>63.06</v>
+        <v>116.76</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2914,25 +2914,25 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7622</v>
+        <v>1.1327</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>14.4</v>
+        <v>23.6</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.312</v>
+        <v>2.388</v>
       </c>
       <c r="W9" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="X9" t="n">
         <v>-1</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>12.06</v>
+        <v>31.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -2973,32 +2973,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>008115</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>天弘中证红利低波动100联接C</t>
+          <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.772</v>
+        <v>1.7771</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>50.73</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>98.66</v>
+        <v>61.75</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6054</v>
+        <v>0.7124</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -3047,37 +3047,37 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>9.6</v>
+        <v>51.4</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.466</v>
+        <v>0.054</v>
       </c>
       <c r="W10" t="n">
-        <v>93.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>13.26</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -3088,20 +3088,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>006476</t>
+          <t>008115</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>南方原油C</t>
+          <t>天弘中证红利低波动100联接C</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.7087</v>
+        <v>1.7718</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3113,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>55.92</v>
+        <v>50.45</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>101.44</v>
+        <v>78.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5722</v>
+        <v>0.6661</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>22.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -3170,29 +3170,29 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2.745</v>
+        <v>0.471</v>
       </c>
       <c r="W11" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>31.68</v>
+        <v>13.26</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -3203,20 +3203,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>513880</t>
+          <t>000369</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>日经225ETF华安</t>
+          <t>广发全球医疗保健指数人民币(QDII)A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.8514</v>
+        <v>2.4316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3228,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>61.3</v>
+        <v>32.42</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -3247,37 +3247,37 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>85.41</v>
+        <v>-6.17</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7781</v>
+        <v>0.0402</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>19.1</v>
+        <v>21.5</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -3285,29 +3285,29 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1.437</v>
+        <v>0.627</v>
       </c>
       <c r="W12" t="n">
-        <v>97</v>
+        <v>77.3</v>
       </c>
       <c r="X12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>27.43</v>
+        <v>14.51</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -3318,20 +3318,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501060</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中金中证优选300指数(LOF)A</t>
+          <t>交银优选回报灵活配置混合C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.3914</v>
+        <v>1.5516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>51.01</v>
+        <v>67.77</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3362,67 +3362,67 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>54.38</v>
+        <v>86.42</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="N13" t="n">
+      <c r="S13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="W13" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="X13" t="n">
         <v>-1</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.7014</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="W13" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>24.8</v>
+        <v>3.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -3433,20 +3433,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>040046</t>
+          <t>159928</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>华安纳斯达克100ETF联接(QDII)A</t>
+          <t>消费ETF汇添富</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.5428</v>
+        <v>2.9856</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>66.95999999999999</v>
+        <v>49.16</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3477,26 +3477,26 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>91.19</v>
+        <v>111.38</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>-1</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
       <c r="Q14" t="n">
-        <v>0.7748</v>
+        <v>0.5689</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -3507,37 +3507,37 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>28.6</v>
+        <v>15.1</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.916</v>
+        <v>0.663</v>
       </c>
       <c r="W14" t="n">
-        <v>97.90000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="AB14" t="n">
         <v>-1</v>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="AA14" t="n">
-        <v>31.24</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -3548,20 +3548,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>000216</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>易方达标普消费品指数A</t>
+          <t>华安黄金ETF联接A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.9556</v>
+        <v>3.5133</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>48.11</v>
+        <v>39.73</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-25.76</v>
+        <v>-12.26</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3611,18 +3611,18 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5478</v>
+        <v>0.0227</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>18.1</v>
+        <v>11.5</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1.069</v>
+        <v>1.125</v>
       </c>
       <c r="W15" t="n">
-        <v>78.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>28.4</v>
+        <v>25.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3663,20 +3663,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>012832</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
+          <t>南方中证新能源ETF联接C</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.7767</v>
+        <v>0.7664</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3688,15 +3688,15 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>72.27</v>
+        <v>61.01</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -3707,15 +3707,15 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>75.38</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7745</v>
+        <v>0.7905</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -3737,21 +3737,21 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>56.5</v>
+        <v>16.4</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.051</v>
+        <v>1.311</v>
       </c>
       <c r="W16" t="n">
-        <v>99.3</v>
+        <v>53</v>
       </c>
       <c r="X16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>1.88</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AB16" t="n">
         <v>1</v>
@@ -3778,20 +3778,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>000369</t>
+          <t>515580</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>广发全球医疗保健指数人民币(QDII)A</t>
+          <t>科技100ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.4878</v>
+        <v>2.709</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>40.52</v>
+        <v>61.41</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3822,67 +3822,67 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-19.52</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.7899</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>18</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="W17" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.1895</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="W17" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="AA17" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.5</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -3893,20 +3893,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>012805</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>广发恒生科技ETF联接(QDII)C</t>
+          <t>中证500ETF易方达</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7929</v>
+        <v>1.651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3918,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>47.55</v>
+        <v>60.5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3937,15 +3937,15 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>8.630000000000001</v>
+        <v>76.63</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.7648</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>15.7</v>
+        <v>17.9</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3975,29 +3975,29 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>1.385</v>
+        <v>1.036</v>
       </c>
       <c r="W18" t="n">
-        <v>47.9</v>
+        <v>93.8</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>53.89</v>
+        <v>38.31</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -4008,20 +4008,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>513880</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>交银优选回报灵活配置混合C</t>
+          <t>日经225ETF华安</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.549</v>
+        <v>1.8466</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>62.18</v>
+        <v>57.06</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>64.88</v>
+        <v>9.23</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7635</v>
+        <v>0.6309</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>21.9</v>
+        <v>20.4</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.074</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>99.5</v>
+        <v>95.8</v>
       </c>
       <c r="X19" t="n">
         <v>-1</v>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>3.91</v>
+        <v>27.43</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -4123,20 +4123,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>510580</t>
+          <t>501060</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中证500ETF易方达</t>
+          <t>中金中证优选300指数(LOF)A</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.6297</v>
+        <v>2.4035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>58.13</v>
+        <v>53.67</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -4167,15 +4167,15 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>67.42</v>
+        <v>66.39</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7692</v>
+        <v>0.7301</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>17.8</v>
+        <v>9.9</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -4205,29 +4205,29 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>1.105</v>
+        <v>0.533</v>
       </c>
       <c r="W20" t="n">
-        <v>91.5</v>
+        <v>93.7</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>38.31</v>
+        <v>24.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>

--- a/fund.xlsx
+++ b/fund.xlsx
@@ -586,52 +586,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.29</v>
+        <v>-0.9</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-5.18</v>
+        <v>-5.07</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9299999999999997</v>
+        <v>-4.27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6199999999999999</v>
+        <v>-0.03000000000000025</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.800000000000001</v>
+        <v>-6.140000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08999999999999986</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="J3" t="n">
-        <v>13.48</v>
+        <v>13.95</v>
       </c>
       <c r="K3" t="n">
-        <v>23.06</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-0.6000000000000001</v>
+        <v>24.74</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2.57</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-6.549999999999999</v>
+        <v>-7.23</v>
       </c>
       <c r="O3" t="n">
-        <v>4.550000000000001</v>
+        <v>1.39</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-12.72</v>
+        <v>-19.67</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-13.74</v>
+        <v>-11.42</v>
       </c>
       <c r="R3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="S3" t="n">
-        <v>16.07</v>
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>20.28</v>
       </c>
       <c r="T3" t="n">
-        <v>2.83</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="4">
@@ -651,52 +651,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.85</v>
+        <v>0.21</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-7.74</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>6.05</v>
+        <v>-3.83</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-2.41</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.86</v>
+        <v>-3.9</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-17.75</v>
+        <v>-14.06</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.74</v>
+        <v>-4.619999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>12.67</v>
+        <v>11.89</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>50.92</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-1.16</v>
+        <v>53.04</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3.68</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>9.670000000000002</v>
+        <v>-5.99</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.25</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-15.2</v>
+        <v>-23.54</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-24.69</v>
+        <v>-19.34</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.75</v>
+        <v>-4.23</v>
       </c>
       <c r="S4" t="n">
-        <v>15.26</v>
+        <v>18.22</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>30.69</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="5">
@@ -716,52 +716,52 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.74</v>
+        <v>-0.16</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-8.59</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.06</v>
+        <v>-9.540000000000001</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-5.88</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-8.109999999999999</v>
+        <v>-11.17</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-24.28</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-14.66</v>
+        <v>-18.52</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-16.54</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.91</v>
+        <v>-2.98</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.449999999999999</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.4299999999999999</v>
+        <v>-5.16</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>3.31</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-9.959999999999999</v>
+        <v>-11.7</v>
       </c>
       <c r="O5" t="n">
-        <v>4.680000000000001</v>
+        <v>-0.2199999999999998</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-21.45</v>
+        <v>-30.81</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-31.22</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-12.67</v>
+        <v>-23.8</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>-16.15</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.32</v>
+        <v>3.35</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-24.68</v>
+        <v>-25.96</v>
       </c>
     </row>
     <row r="6">
@@ -780,53 +780,53 @@
           <t>101.98</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0.8800000000000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.6199999999999992</v>
+      <c r="D6" s="3" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6.53</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.54</v>
+        <v>-3.52</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>9.42</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>29.85</v>
+        <v>27.64</v>
       </c>
       <c r="I6" t="n">
-        <v>3.43</v>
+        <v>4.92</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.44</v>
+        <v>-7.82</v>
       </c>
       <c r="K6" t="n">
-        <v>15.88</v>
+        <v>17.58</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5700000000000001</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.75</v>
+        <v>1.01</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>4.37</v>
       </c>
       <c r="O6" t="n">
-        <v>1.910000000000001</v>
+        <v>2.14</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-8.800000000000001</v>
+        <v>-10.22</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>22.91</v>
+        <v>22.36</v>
       </c>
       <c r="R6" t="n">
-        <v>5.42</v>
+        <v>5.309999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.85</v>
+        <v>-1.49</v>
       </c>
       <c r="T6" t="n">
-        <v>-4.35</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="7">
@@ -845,52 +845,52 @@
           <t>132.24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>6.09</v>
+      <c r="D7" s="3" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4100000000000001</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>37.59999999999999</v>
+        <v>34.19</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-17.85</v>
+        <v>-18.32</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-23.93</v>
+        <v>-25.39</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-2.669999999999999</v>
+      <c r="M7" t="n">
+        <v>0.1999999999999997</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-6.04</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>-13.75</v>
+        <v>-14.44</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>30.66</v>
+        <v>28.91</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-15.86</v>
+        <v>-17.93</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-21.34</v>
+        <v>-19.06</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -938,29 +938,29 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
-        <v>-0.3100000000000001</v>
+      <c r="M8" s="2" t="n">
+        <v>3.47</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.369999999999999</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.620000000000001</v>
+        <v>-2.16</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>5.66</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-13.34</v>
+        <v>-19.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.940000000000001</v>
+        <v>-5.280000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>1.99</v>
+        <v>0.3899999999999988</v>
       </c>
       <c r="S8" t="n">
-        <v>2.59</v>
+        <v>6.33</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-20.23</v>
+        <v>-20.8</v>
       </c>
     </row>
     <row r="9">
@@ -979,29 +979,29 @@
           <t>2637.86</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>0.3100000000000001</v>
+      <c r="D9" s="3" t="n">
+        <v>-3.47</v>
       </c>
       <c r="E9" t="n">
-        <v>1.369999999999999</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-3.620000000000001</v>
+        <v>2.16</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-5.66</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>13.34</v>
+        <v>19.64</v>
       </c>
       <c r="H9" t="n">
-        <v>6.940000000000001</v>
+        <v>5.280000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.99</v>
+        <v>-0.3899999999999988</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.59</v>
+        <v>-6.33</v>
       </c>
       <c r="K9" t="n">
-        <v>20.23</v>
+        <v>20.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1041,56 +1041,56 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>380.36</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.43</v>
+          <t>380.48</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1.76</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-4.47</v>
+        <v>7.44</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-8.550000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>4.52</v>
+        <v>-3.149999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4799999999999995</v>
+        <v>-0.2799999999999994</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>44.27</v>
-      </c>
-      <c r="K10" t="n">
-        <v>16.93</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.12</v>
+        <v>34.31</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>5.23</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>6.470000000000001</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-2.479999999999999</v>
+        <v>5.279999999999999</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>10.59</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-17.81</v>
+        <v>-28.19</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.420000000000002</v>
+        <v>-8.43</v>
       </c>
       <c r="R10" t="n">
-        <v>1.510000000000001</v>
+        <v>0.1099999999999994</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>46.86</v>
+        <v>40.64</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.3</v>
+        <v>16.72</v>
       </c>
     </row>
     <row r="11">
@@ -1106,56 +1106,56 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>572.21</t>
+          <t>574.57</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>3.109999999999999</v>
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.95</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.470000000000001</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-2.05</v>
+        <v>0.6299999999999999</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-6.050000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.98</v>
+        <v>-5.91</v>
       </c>
       <c r="I11" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>31.55</v>
-      </c>
-      <c r="K11" t="n">
-        <v>22.64</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-0.8200000000000001</v>
+        <v>27.26</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>3.79</v>
       </c>
       <c r="N11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.1500000000000004</v>
+        <v>0.7899999999999996</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>6.29</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-15.39</v>
+        <v>-25.69</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-11.92</v>
+        <v>-11.19</v>
       </c>
       <c r="R11" t="n">
-        <v>3.67</v>
+        <v>1.969999999999999</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>34.14</v>
+        <v>33.59</v>
       </c>
       <c r="T11" t="n">
-        <v>2.41</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="12">
@@ -1175,51 +1175,51 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.4399999999999999</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>-3.87</v>
+        <v>-1.03</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.94</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-13.56</v>
+        <v>-7.6</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-7.12</v>
+        <v>-14.83</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-13.12</v>
+        <v>-15.78</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>28.9</v>
+        <v>27.34</v>
       </c>
       <c r="J12" t="n">
-        <v>4.86</v>
+        <v>7.01</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>-0.75</v>
+      <c r="M12" s="2" t="n">
+        <v>2.44</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>-5.239999999999999</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>-9.939999999999998</v>
+        <v>-4.100000000000001</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-1.94</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>-20.46</v>
+        <v>-34.47</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>-20.06</v>
+        <v>-21.06</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>30.89</v>
+        <v>27.73</v>
       </c>
       <c r="S12" t="n">
-        <v>7.45</v>
+        <v>13.34</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1243,53 +1243,53 @@
           <t>1071.35</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>-3.24</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-6.720000000000001</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-1.16</v>
+      <c r="D13" t="n">
+        <v>-0.1900000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-12.85</v>
       </c>
       <c r="G13" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>-23.3</v>
+        <v>-2.850000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-4.25</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.93</v>
+        <v>-13.34</v>
       </c>
       <c r="J13" t="n">
-        <v>13.06</v>
+        <v>11.35</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>37.93</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>-3.55</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>-8.09</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.460000000000001</v>
+        <v>42.23999999999999</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>-7.19</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>-30.24</v>
+        <v>-22.49</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-9.530000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>-2.94</v>
+        <v>-12.95</v>
       </c>
       <c r="S13" t="n">
-        <v>15.65</v>
+        <v>17.68</v>
       </c>
       <c r="T13" t="n">
-        <v>17.7</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="14">
@@ -1308,53 +1308,53 @@
           <t>9.80</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>-3.8</v>
+      <c r="D14" t="n">
+        <v>1.06</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.63</v>
+        <v>-0.2</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-7.31</v>
+        <v>-13.01</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.08</v>
+        <v>-5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>-11.38</v>
+        <v>-12.16</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.58</v>
+        <v>-4.64</v>
       </c>
       <c r="J14" t="n">
-        <v>3.600000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>25.51</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>-4.11</v>
+        <v>28.9</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>4.529999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.999999999999999</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-3.69</v>
+        <v>-2.36</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>-7.35</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-17.42</v>
+        <v>-24.64</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>-18.32</v>
+        <v>-17.44</v>
       </c>
       <c r="R14" t="n">
-        <v>-6.59</v>
+        <v>-4.250000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>6.19</v>
+        <v>7.16</v>
       </c>
       <c r="T14" t="n">
-        <v>5.279999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="15">
@@ -1374,51 +1374,51 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.3200000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5199999999999996</v>
+        <v>2.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9900000000000002</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4.989999999999999</v>
+        <v>-4.5</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>10.65</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.25</v>
+        <v>-5.69</v>
       </c>
       <c r="I15" t="n">
-        <v>2.58</v>
+        <v>0.3200000000000003</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>23.76</v>
+        <v>21.83</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>0.01000000000000001</v>
+      <c r="M15" s="2" t="n">
+        <v>4.24</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8499999999999996</v>
+        <v>0.7399999999999998</v>
       </c>
       <c r="O15" t="n">
-        <v>2.630000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-8.350000000000001</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-8.190000000000001</v>
+        <v>-8.99</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>-10.97</v>
       </c>
       <c r="R15" t="n">
-        <v>4.57</v>
+        <v>0.7099999999999991</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>26.35</v>
+        <v>28.16</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1439,56 +1439,56 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>380.36</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.73</v>
+          <t>380.48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>3.2</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7.390000000000001</v>
+        <v>4.86</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.800000000000001</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-1.52</v>
+        <v>-2.83</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>9.94</v>
       </c>
       <c r="H16" t="n">
-        <v>7.080000000000002</v>
+        <v>0.6499999999999986</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.02</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>25.68</v>
+        <v>-3.049999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15.36</v>
       </c>
       <c r="K16" t="n">
-        <v>6.859999999999999</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>6.020000000000001</v>
+        <v>18.72</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8200000000000003</v>
+        <v>2.83</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-14.86</v>
+        <v>-9.700000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1400000000000006</v>
+        <v>-4.630000000000003</v>
       </c>
       <c r="R16" t="n">
-        <v>-3.029999999999999</v>
+        <v>-2.66</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>28.27</v>
+        <v>21.69</v>
       </c>
       <c r="T16" t="n">
-        <v>-13.37</v>
+        <v>-2.080000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1508,52 +1508,52 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-5.86</v>
+        <v>-1.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-2.64</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-7.140000000000001</v>
+        <v>-13.88</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>24.22</v>
+        <v>15.76</v>
       </c>
       <c r="H17" t="n">
-        <v>-7.970000000000002</v>
+        <v>4.059999999999999</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>32.86</v>
+        <v>25.29</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>30.01</v>
+        <v>26.87</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>35.92</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>-3.17</v>
+        <v>37.6</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>1.67</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-7.23</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-3.52</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>-14.91</v>
+        <v>-4.800000000000001</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-3.880000000000003</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1.220000000000002</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>34.84999999999999</v>
+        <v>25.68</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>32.6</v>
+        <v>33.2</v>
       </c>
       <c r="T17" t="n">
-        <v>15.69</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="18">
@@ -1572,53 +1572,53 @@
           <t>294.30</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>11.58</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-9.370000000000001</v>
+      <c r="D18" s="3" t="n">
+        <v>-8.74</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.65</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>51.44</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4.56</v>
+        <v>46.78</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>7.039999999999999</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>-24.5</v>
+        <v>-20.25</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-23</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>26.02</v>
+        <v>-22.88</v>
+      </c>
+      <c r="J18" t="n">
+        <v>18.98</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>64.31</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>-10.74</v>
+        <v>68.05</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.4899999999999998</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>55.06</v>
+        <v>52.44</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>-8.780000000000001</v>
+        <v>-12.6</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>-31.44</v>
+        <v>-25.53</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>-21.01</v>
+        <v>-22.49</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>28.61</v>
+        <v>25.31</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>44.08000000000001</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="22">
@@ -1767,52 +1767,52 @@
           <t>146.66</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1.38</v>
+      <c r="D24" s="3" t="n">
+        <v>-0.8500000000000001</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.9600000000000001</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-2.81</v>
+        <v>-1.95</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4.739999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>13.54</v>
+        <v>11.23</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-5.83</v>
+        <v>-1.65</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>1.22</v>
+      <c r="M24" s="3" t="n">
+        <v>-0.5800000000000001</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>-0.93</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-1.96</v>
+        <v>-1.37</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>4.029999999999999</v>
+        <v>5.43</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>10.54</v>
+        <v>8.620000000000001</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.01</v>
+        <v>9.68</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>4.53</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -1860,29 +1860,29 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>-0.1599999999999999</v>
+      <c r="M25" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.03</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0.8500000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.82</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-3</v>
+        <v>-2.61</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>3.21</v>
+        <v>2.68</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>6.84</v>
+        <v>6.18</v>
       </c>
       <c r="T25" t="n">
-        <v>4.180000000000001</v>
+        <v>5.219999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2053,20 +2053,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>159928</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>易方达标普消费品指数A</t>
+          <t>消费ETF汇添富</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.874</v>
+        <v>2.7484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>39.82</v>
+        <v>34.68</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2097,52 +2097,52 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-16.54</v>
+        <v>23.57</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0.1962</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>空头</t>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>28.4</v>
+        <v>51.23</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -2168,20 +2168,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>513880</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>沪深300ETF易方达</t>
+          <t>日经225ETF华安</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.4635</v>
+        <v>2.0615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>64.7</v>
+        <v>66.87</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2212,37 +2212,37 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>89.53</v>
+        <v>109.13</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7654</v>
+        <v>0.9041</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>21.4</v>
+        <v>24.2</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.608</v>
+        <v>1.398</v>
       </c>
       <c r="W3" t="n">
-        <v>83.8</v>
+        <v>100</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>36.33</v>
+        <v>27.42</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>-2.5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -2283,20 +2283,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>050025</t>
+          <t>501060</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>中金中证优选300指数(LOF)A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.3346</v>
+        <v>2.316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>66.06999999999999</v>
+        <v>39.89</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2327,15 +2327,15 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>86.52</v>
+        <v>35.69</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7137</v>
+        <v>0.2434</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2357,37 +2357,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>29.8</v>
+        <v>20.1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.641</v>
       </c>
       <c r="W4" t="n">
-        <v>99.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>18.73</v>
+        <v>24.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -2398,20 +2398,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>040046</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>华安纳斯达克100ETF联接(QDII)A</t>
+          <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.7762</v>
+        <v>1.7859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2423,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>71.91</v>
+        <v>80.94</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2442,26 +2442,26 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>96.70999999999999</v>
+        <v>103.64</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8249</v>
+        <v>1.0156</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>-1</v>
       </c>
       <c r="T5" t="n">
-        <v>32.6</v>
+        <v>45.6</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.917</v>
+        <v>0.048</v>
       </c>
       <c r="W5" t="n">
         <v>100</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>31.24</v>
+        <v>1.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>011555</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>海富通欣利混合C</t>
+          <t>交银优选回报灵活配置混合C</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.4531</v>
+        <v>1.5541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>58.98</v>
+        <v>56.14</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>73.5</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7877</v>
+        <v>0.4448</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>14.8</v>
+        <v>22.9</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.286</v>
+        <v>0.064</v>
       </c>
       <c r="W6" t="n">
-        <v>96.5</v>
+        <v>98.5</v>
       </c>
       <c r="X6" t="n">
         <v>-1</v>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>12.06</v>
+        <v>3.91</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -2628,60 +2628,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>012805</t>
+          <t>012832</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>广发恒生科技ETF联接(QDII)C</t>
+          <t>南方中证新能源ETF联接C</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7874</v>
+        <v>0.7294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="N7" t="n">
         <v>-1</v>
       </c>
-      <c r="G7" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>持有</t>
@@ -2691,18 +2691,18 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.453</v>
+        <v>0.0827</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>13.2</v>
+        <v>10.8</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.369</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>46.9</v>
+        <v>47.9</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -2725,14 +2725,14 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>53.89</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -2743,20 +2743,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>159687</t>
+          <t>000369</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>亚太精选ETF南方</t>
+          <t>广发全球医疗保健指数人民币(QDII)A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.7286</v>
+        <v>2.5215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>60.05</v>
+        <v>58.87</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>80.56999999999999</v>
+        <v>101.21</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2799,25 +2799,25 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7353</v>
+        <v>0.9433</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>17.5</v>
+        <v>13.8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>95.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="X8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2840,14 +2840,14 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>15.3</v>
+        <v>14.51</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -2858,20 +2858,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>006476</t>
+          <t>510310</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南方原油C</t>
+          <t>沪深300ETF易方达</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.9146</v>
+        <v>2.5085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2883,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>68.78</v>
+        <v>56.13</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>116.76</v>
+        <v>86.97</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2914,25 +2914,25 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.1327</v>
+        <v>0.5566</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>23.6</v>
+        <v>20.6</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2940,13 +2940,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>2.388</v>
+        <v>0.709</v>
       </c>
       <c r="W9" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="X9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>31.68</v>
+        <v>36.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -2973,20 +2973,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>515580</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
+          <t>科技100ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.7771</v>
+        <v>2.856</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2998,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>67.23999999999999</v>
+        <v>54.41</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3010,22 +3010,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="L10" t="n">
-        <v>61.75</v>
+        <v>45.81</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7124</v>
+        <v>0.5222</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>51.4</v>
+        <v>25.8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -3055,13 +3055,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.054</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>99.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="X10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>1.88</v>
+        <v>38.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>-0.5</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -3088,20 +3088,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>008115</t>
+          <t>040046</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>天弘中证红利低波动100联接C</t>
+          <t>华安纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.7718</v>
+        <v>8.539099999999999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3113,15 +3113,15 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>50.45</v>
+        <v>76.09</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>78.7</v>
+        <v>103.65</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3144,55 +3144,55 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6661</v>
+        <v>0.8685</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T11" t="n">
-        <v>8.300000000000001</v>
+        <v>43.3</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.471</v>
+        <v>0.798</v>
       </c>
       <c r="W11" t="n">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>13.26</v>
+        <v>31.24</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -3203,20 +3203,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>000369</t>
+          <t>159687</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>广发全球医疗保健指数人民币(QDII)A</t>
+          <t>亚太精选ETF南方</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.4316</v>
+        <v>1.8249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3228,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>32.42</v>
+        <v>61.55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.17</v>
+        <v>107.53</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3259,25 +3259,25 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0402</v>
+        <v>0.6979</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>21.5</v>
+        <v>20.7</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -3285,29 +3285,29 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.627</v>
+        <v>1.016</v>
       </c>
       <c r="W12" t="n">
-        <v>77.3</v>
+        <v>98.8</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>14.51</v>
+        <v>15.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -3318,32 +3318,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>交银优选回报灵活配置混合C</t>
+          <t>中证500ETF易方达</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.5516</v>
+        <v>1.6571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G13" t="n">
-        <v>67.77</v>
+        <v>46.39</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3362,37 +3362,37 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>86.42</v>
+        <v>15.85</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>买入</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.8115</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
       <c r="S13" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>24.2</v>
+        <v>17.4</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3400,13 +3400,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.06900000000000001</v>
+        <v>1.298</v>
       </c>
       <c r="W13" t="n">
-        <v>99.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>3.91</v>
+        <v>38.31</v>
       </c>
       <c r="AB13" t="n">
         <v>-0.5</v>
@@ -3433,20 +3433,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>012805</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>消费ETF汇添富</t>
+          <t>广发恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.9856</v>
+        <v>0.7844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>49.16</v>
+        <v>45.41</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>111.38</v>
+        <v>73.39</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3489,14 +3489,14 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5689</v>
+        <v>0.3076</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>15.1</v>
+        <v>11.2</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.663</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>10.4</v>
+        <v>46.4</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>51.23</v>
+        <v>53.89</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -3548,20 +3548,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>000216</t>
+          <t>006476</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>华安黄金ETF联接A</t>
+          <t>南方原油C</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.5133</v>
+        <v>1.7423</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>39.73</v>
+        <v>43.98</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-12.26</v>
+        <v>-21.99</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0227</v>
+        <v>0.0751</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>11.5</v>
+        <v>17.6</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3630,26 +3630,26 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1.125</v>
+        <v>2.092</v>
       </c>
       <c r="W15" t="n">
-        <v>74.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>25.07</v>
+        <v>31.68</v>
       </c>
       <c r="AB15" t="n">
         <v>2.5</v>
@@ -3663,20 +3663,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>012832</t>
+          <t>050025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>南方中证新能源ETF联接C</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7664</v>
+        <v>5.6087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3688,15 +3688,15 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>61.01</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -3707,51 +3707,51 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>79.40000000000001</v>
+        <v>106.05</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7905</v>
+        <v>0.841</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T16" t="n">
-        <v>16.4</v>
+        <v>37</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1.311</v>
+        <v>0.472</v>
       </c>
       <c r="W16" t="n">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>65.01000000000001</v>
+        <v>18.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -3778,20 +3778,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>515580</t>
+          <t>011555</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>科技100ETF华泰柏瑞</t>
+          <t>海富通欣利混合C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.709</v>
+        <v>1.4358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>61.41</v>
+        <v>40.26</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3822,37 +3822,37 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>95.06999999999999</v>
+        <v>15.62</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>买入</t>
         </is>
       </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.7899</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T17" t="n">
-        <v>18</v>
+        <v>12.9</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3860,29 +3860,29 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1.078</v>
+        <v>0.283</v>
       </c>
       <c r="W17" t="n">
-        <v>95.59999999999999</v>
+        <v>93</v>
       </c>
       <c r="X17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
       <c r="AA17" t="n">
-        <v>38.9</v>
+        <v>12.06</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -3893,20 +3893,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>510580</t>
+          <t>118002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中证500ETF易方达</t>
+          <t>易方达标普消费品指数A</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.651</v>
+        <v>2.9814</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3918,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>60.5</v>
+        <v>56.76</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3937,37 +3937,37 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>76.63</v>
+        <v>113.74</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7648</v>
+        <v>0.8635</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>17.9</v>
+        <v>11.4</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>1.036</v>
+        <v>0.844</v>
       </c>
       <c r="W18" t="n">
-        <v>93.8</v>
+        <v>79.3</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -3990,14 +3990,14 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>38.31</v>
+        <v>28.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>-2.5</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -4008,20 +4008,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>513880</t>
+          <t>008115</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>日经225ETF华安</t>
+          <t>天弘中证红利低波动100联接C</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.8466</v>
+        <v>1.7483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>57.06</v>
+        <v>48.71</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -4052,15 +4052,15 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9.23</v>
+        <v>56.85</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6309</v>
+        <v>0.4447</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>20.4</v>
+        <v>15.3</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4090,29 +4090,29 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>1.29</v>
+        <v>0.507</v>
       </c>
       <c r="W19" t="n">
-        <v>95.8</v>
+        <v>91.2</v>
       </c>
       <c r="X19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>27.43</v>
+        <v>13.26</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -4123,20 +4123,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>501060</t>
+          <t>000216</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中金中证优选300指数(LOF)A</t>
+          <t>华安黄金ETF联接A</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.4035</v>
+        <v>3.413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>53.67</v>
+        <v>40.13</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -4167,15 +4167,15 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>66.39</v>
+        <v>42.79</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7301</v>
+        <v>0.2352</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>9.9</v>
+        <v>20.1</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.533</v>
+        <v>1.022</v>
       </c>
       <c r="W20" t="n">
-        <v>93.7</v>
+        <v>70.5</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>24.8</v>
+        <v>25.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>

--- a/fund.xlsx
+++ b/fund.xlsx
@@ -586,52 +586,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.9</v>
+        <v>0.73</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-5.07</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-4.27</v>
+        <v>-5.57</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>-5.26</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.03000000000000025</v>
+        <v>0.74</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.140000000000001</v>
+        <v>-6.330000000000002</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1000000000000014</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>13.95</v>
+        <v>12.92</v>
       </c>
       <c r="K3" t="n">
-        <v>24.74</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>2.57</v>
+        <v>24.21</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.46</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-7.23</v>
+        <v>-4.01</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>-2.47</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-19.67</v>
+        <v>-15.16</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-11.42</v>
+        <v>-10.92</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4900000000000002</v>
+        <v>0.3300000000000001</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>20.28</v>
+        <v>20.26</v>
       </c>
       <c r="T3" t="n">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="4">
@@ -651,52 +651,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.21</v>
+        <v>0.98</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-3.83</v>
+        <v>-3.3</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.41</v>
+        <v>-3.8</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.9</v>
+        <v>-2.33</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-14.06</v>
+        <v>-14.53</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.619999999999999</v>
+        <v>-2.73</v>
       </c>
       <c r="J4" t="n">
-        <v>11.89</v>
+        <v>9.43</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>53.04</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-5.99</v>
+        <v>52.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-1.74</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>-1.01</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-23.54</v>
+        <v>-18.23</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-19.34</v>
+        <v>-19.12</v>
       </c>
       <c r="R4" t="n">
-        <v>-4.23</v>
+        <v>-3.23</v>
       </c>
       <c r="S4" t="n">
-        <v>18.22</v>
+        <v>16.77</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>32.24</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="5">
@@ -715,53 +715,53 @@
           <t>553.76</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>-0.16</v>
+      <c r="D5" s="3" t="n">
+        <v>-2.81</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-9.540000000000001</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-5.88</v>
+        <v>-4.75</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-11.17</v>
+        <v>-8.35</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-18.52</v>
+        <v>-22.03</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-16.54</v>
+        <v>-16.27</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.98</v>
+        <v>-1.74</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>3.31</v>
+        <v>-7.880000000000003</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>-3.08</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-11.7</v>
+        <v>-8.32</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2199999999999998</v>
+        <v>-1.96</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-30.81</v>
+        <v>-24.25</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-23.8</v>
+        <v>-26.62</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-16.15</v>
+        <v>-16.77</v>
       </c>
       <c r="S5" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-25.96</v>
+        <v>-28.71</v>
       </c>
     </row>
     <row r="6">
@@ -780,53 +780,53 @@
           <t>101.98</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>-2.46</v>
+      <c r="D6" t="n">
+        <v>-0.26</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6.53</v>
+        <v>3.49</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.52</v>
+        <v>-1.98</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>9.42</v>
+        <v>7.48</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>27.64</v>
+        <v>26.7</v>
       </c>
       <c r="I6" t="n">
-        <v>4.92</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.82</v>
+        <v>-7.540000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>17.58</v>
+        <v>20.16</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>-0.53</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.37</v>
+        <v>5.05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.14</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-10.22</v>
+        <v>-8.42</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>22.36</v>
+        <v>22.11</v>
       </c>
       <c r="R6" t="n">
-        <v>5.309999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.49</v>
+        <v>-0.2000000000000011</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.22</v>
+        <v>-0.6700000000000004</v>
       </c>
     </row>
     <row r="7">
@@ -846,51 +846,51 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-3.27</v>
+        <v>-3.95</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-3.88</v>
+        <v>-6.75</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="G7" t="n">
-        <v>5.199999999999999</v>
+        <v>6.790000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>34.19</v>
+        <v>31.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-18.32</v>
+        <v>-18.57</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-25.39</v>
+        <v>-24.12</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>0.1999999999999997</v>
+      <c r="M7" s="3" t="n">
+        <v>-4.22</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-6.04</v>
+        <v>-5.19</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>-14.44</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>28.91</v>
+        <v>26.81</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-17.93</v>
+        <v>-19.07</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-19.06</v>
+        <v>-16.78</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -938,29 +938,29 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="2" t="n">
-        <v>3.47</v>
+      <c r="M8" t="n">
+        <v>-0.27</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.16</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>5.66</v>
+        <v>1.56</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.79</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-19.64</v>
+        <v>-15.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.280000000000001</v>
+        <v>-4.59</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3899999999999988</v>
+        <v>-0.5</v>
       </c>
       <c r="S8" t="n">
-        <v>6.33</v>
+        <v>7.34</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-20.8</v>
+        <v>-20.83</v>
       </c>
     </row>
     <row r="9">
@@ -979,29 +979,29 @@
           <t>2637.86</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>-3.47</v>
+      <c r="D9" t="n">
+        <v>0.27</v>
       </c>
       <c r="E9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-5.66</v>
+        <v>-1.56</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-2.79</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>19.64</v>
+        <v>15.9</v>
       </c>
       <c r="H9" t="n">
-        <v>5.280000000000001</v>
+        <v>4.59</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3899999999999988</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.33</v>
+        <v>-7.34</v>
       </c>
       <c r="K9" t="n">
-        <v>20.8</v>
+        <v>20.83</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1045,52 +1045,52 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7.44</v>
+        <v>7.59</v>
       </c>
       <c r="F10" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>-8.550000000000001</v>
+        <v>4.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-5.91</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.149999999999999</v>
+        <v>-5.610000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2799999999999994</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>34.31</v>
+        <v>31.09</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>37.52</v>
+        <v>37.9</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5.23</v>
+        <v>1.77</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>5.279999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>10.59</v>
+        <v>7.69</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-28.19</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-8.43</v>
+        <v>-21.81</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>-10.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1099999999999994</v>
+        <v>1.5</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>40.64</v>
+        <v>38.43</v>
       </c>
       <c r="T10" t="n">
-        <v>16.72</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="11">
@@ -1109,53 +1109,53 @@
           <t>574.57</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>0.3200000000000001</v>
+      <c r="D11" s="2" t="n">
+        <v>1.71</v>
       </c>
       <c r="E11" t="n">
-        <v>2.95</v>
+        <v>2.21</v>
       </c>
       <c r="F11" t="n">
         <v>0.6299999999999999</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>-6.050000000000001</v>
+      <c r="G11" t="n">
+        <v>-3.71</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.91</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.58</v>
+        <v>2.34</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>27.26</v>
+        <v>25.27</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>34.02</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.7899999999999996</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>6.29</v>
+        <v>34.47</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.42</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-25.69</v>
+        <v>-19.61</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-11.19</v>
+        <v>-12.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.969999999999999</v>
+        <v>1.84</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>33.59</v>
+        <v>32.61</v>
       </c>
       <c r="T11" t="n">
-        <v>13.22</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="12">
@@ -1174,52 +1174,52 @@
           <t>509.35</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>-1.03</v>
+      <c r="D12" s="2" t="n">
+        <v>1.52</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>-7.6</v>
+        <v>-2.31</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-2.71</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-14.83</v>
+        <v>-19.04</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-15.78</v>
+        <v>-16.03</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>27.34</v>
+        <v>25.25</v>
       </c>
       <c r="J12" t="n">
-        <v>7.01</v>
+        <v>3.52</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>-4.100000000000001</v>
+      <c r="M12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.94</v>
+        <v>0.07999999999999996</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>-34.47</v>
+        <v>-34.94</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>-21.06</v>
+        <v>-20.62</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>27.73</v>
+        <v>24.75</v>
       </c>
       <c r="S12" t="n">
-        <v>13.34</v>
+        <v>10.86</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1244,52 +1244,52 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1900000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="E13" t="n">
-        <v>1.01</v>
+        <v>-0.28</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-12.85</v>
+        <v>-10.85</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.850000000000001</v>
+        <v>-1.13</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.25</v>
+        <v>-8.630000000000003</v>
       </c>
       <c r="I13" t="n">
-        <v>-13.34</v>
+        <v>-14.6</v>
       </c>
       <c r="J13" t="n">
-        <v>11.35</v>
+        <v>11.95</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>42.23999999999999</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>3.28</v>
+        <v>44.15</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.17</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.15</v>
+        <v>1.28</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-7.19</v>
+        <v>-8.06</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-22.49</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-9.530000000000001</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-12.95</v>
+        <v>-17.03</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>-13.22</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>-15.1</v>
       </c>
       <c r="S13" t="n">
-        <v>17.68</v>
+        <v>19.29</v>
       </c>
       <c r="T13" t="n">
-        <v>21.44</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="14">
@@ -1309,52 +1309,52 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.06</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2</v>
+        <v>0.9800000000000002</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-13.01</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-5</v>
+        <v>-9.48</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-8.33</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>-12.16</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.64</v>
+        <v>-5.87</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8300000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>4.529999999999999</v>
+        <v>28.37</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1299999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.36</v>
+        <v>2.54</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>-7.35</v>
+        <v>-6.69</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-24.64</v>
+        <v>-24.23</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>-17.44</v>
+        <v>-16.75</v>
       </c>
       <c r="R14" t="n">
-        <v>-4.250000000000001</v>
+        <v>-6.37</v>
       </c>
       <c r="S14" t="n">
-        <v>7.16</v>
+        <v>8.67</v>
       </c>
       <c r="T14" t="n">
-        <v>8.1</v>
+        <v>7.539999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1373,26 +1373,26 @@
           <t>294.30</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.9</v>
+      <c r="D15" s="2" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>5.52</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>10.65</v>
+        <v>1.93</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.77</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.69</v>
+        <v>-6.530000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3200000000000003</v>
+        <v>1.67</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>21.83</v>
+        <v>21.01</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1400,25 +1400,25 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.7399999999999998</v>
+        <v>4.32</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>7.08</v>
       </c>
       <c r="O15" t="n">
-        <v>1.16</v>
+        <v>4.72</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-8.99</v>
+        <v>-14.13</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>-10.97</v>
+        <v>-11.12</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7099999999999991</v>
+        <v>1.17</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>28.16</v>
+        <v>28.35</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1443,52 +1443,52 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.86</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>9.94</v>
+        <v>1.33</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.02</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6499999999999986</v>
+        <v>1.959999999999997</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.049999999999999</v>
+        <v>-6.14</v>
       </c>
       <c r="J16" t="n">
-        <v>15.36</v>
+        <v>13.37</v>
       </c>
       <c r="K16" t="n">
-        <v>18.72</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.7</v>
+        <v>22.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>11.27</v>
       </c>
       <c r="O16" t="n">
-        <v>2.83</v>
+        <v>4.12</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-9.700000000000001</v>
+        <v>-11.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.630000000000003</v>
+        <v>-2.630000000000003</v>
       </c>
       <c r="R16" t="n">
-        <v>-2.66</v>
+        <v>-6.64</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>21.69</v>
+        <v>20.71</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.080000000000001</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="17">
@@ -1507,53 +1507,53 @@
           <t>2131.63</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-2.64</v>
+      <c r="D17" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-4.78</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-13.88</v>
+        <v>-15.46</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>15.76</v>
+        <v>18.16</v>
       </c>
       <c r="H17" t="n">
-        <v>4.059999999999999</v>
+        <v>1.289999999999999</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>25.29</v>
+        <v>28.83000000000001</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>26.87</v>
+        <v>25.99</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>1.67</v>
+        <v>39.27</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1299999999999999</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-4.800000000000001</v>
+        <v>-3.22</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-8.220000000000001</v>
+        <v>-12.67</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.880000000000003</v>
+        <v>2.260000000000002</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.220000000000002</v>
+        <v>-3.300000000000001</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>25.68</v>
+        <v>28.33000000000001</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>33.2</v>
+        <v>33.33</v>
       </c>
       <c r="T17" t="n">
-        <v>16.8</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="18">
@@ -1572,53 +1572,53 @@
           <t>294.30</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>-8.74</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2.65</v>
+      <c r="D18" s="2" t="n">
+        <v>4.029999999999999</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-10.99</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>46.78</v>
+        <v>38.23999999999999</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>7.039999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>-20.25</v>
+        <v>-21.81</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-22.88</v>
+        <v>-16.92</v>
       </c>
       <c r="J18" t="n">
-        <v>18.98</v>
+        <v>13.57</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>68.05</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>-5.27</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.4899999999999998</v>
+        <v>60.78</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>-9.43</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>52.44</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>-12.6</v>
+        <v>41.03</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.699999999999999</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>-25.53</v>
+        <v>-26.4</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>-22.49</v>
+        <v>-17.42</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>25.31</v>
+        <v>20.91</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>47.25</v>
+        <v>39.95</v>
       </c>
     </row>
     <row r="22">
@@ -1768,25 +1768,25 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-0.8500000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-0.9600000000000001</v>
+        <v>-1.69</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-1.95</v>
+        <v>-0.59</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>6.25</v>
+        <v>3.66</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>11.23</v>
+        <v>11.76</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7.000000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-1.65</v>
+        <v>-3.11</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1794,25 +1794,25 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>-0.5800000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>-0.93</v>
+        <v>-1.36</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-1.37</v>
+        <v>-0.36</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>5.43</v>
+        <v>3.470000000000001</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>8.620000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>9.68</v>
+        <v>11.36</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>4.53</v>
+        <v>3.21</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -1861,28 +1861,28 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O25" s="2" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.1</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.23</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.1899999999999999</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-2.61</v>
+        <v>-2.99</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>6.18</v>
+        <v>6.32</v>
       </c>
       <c r="T25" t="n">
-        <v>5.219999999999999</v>
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
@@ -2053,20 +2053,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>000369</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>消费ETF汇添富</t>
+          <t>广发全球医疗保健指数人民币(QDII)A</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.7484</v>
+        <v>2.4874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>34.68</v>
+        <v>51.19</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2097,15 +2097,15 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>23.57</v>
+        <v>67.59</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2745</v>
+        <v>0.6214</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -2127,21 +2127,21 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>37.9</v>
+        <v>12.6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>0.858</v>
+        <v>0.792</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>51.23</v>
+        <v>14.51</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -2168,20 +2168,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>513880</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>日经225ETF华安</t>
+          <t>中证500ETF易方达</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.0615</v>
+        <v>1.5791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>66.87</v>
+        <v>34.93</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>109.13</v>
+        <v>-6.74</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -2224,25 +2224,25 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9041</v>
+        <v>-0.1453</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>24.2</v>
+        <v>15.9</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -2250,29 +2250,29 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>1.398</v>
+        <v>1.341</v>
       </c>
       <c r="W3" t="n">
-        <v>100</v>
+        <v>80.5</v>
       </c>
       <c r="X3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>27.42</v>
+        <v>38.31</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -2283,20 +2283,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>501060</t>
+          <t>040046</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中金中证优选300指数(LOF)A</t>
+          <t>华安纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.316</v>
+        <v>8.170299999999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>39.89</v>
+        <v>48.4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2327,67 +2327,67 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>35.69</v>
+        <v>24.45</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>买入</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="S4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.2434</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
       <c r="T4" t="n">
-        <v>20.1</v>
+        <v>42.4</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.641</v>
+        <v>1.026</v>
       </c>
       <c r="W4" t="n">
-        <v>86.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>24.8</v>
+        <v>31.24</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -2398,20 +2398,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>050025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.7859</v>
+        <v>5.6182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2423,15 +2423,15 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>80.94</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>103.64</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -2454,25 +2454,25 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.0156</v>
+        <v>0.7856</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>45.6</v>
+        <v>37.5</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.048</v>
+        <v>0.425</v>
       </c>
       <c r="W5" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="X5" t="n">
         <v>-1</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>1.88</v>
+        <v>18.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>513880</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>交银优选回报灵活配置混合C</t>
+          <t>日经225ETF华安</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.5541</v>
+        <v>2.065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>56.14</v>
+        <v>61.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2557,15 +2557,15 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>80.51000000000001</v>
+        <v>84.16</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4448</v>
+        <v>0.7313</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2587,18 +2587,18 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>22.9</v>
+        <v>26.9</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.064</v>
+        <v>1.357</v>
       </c>
       <c r="W6" t="n">
-        <v>98.5</v>
+        <v>95.8</v>
       </c>
       <c r="X6" t="n">
         <v>-1</v>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>3.91</v>
+        <v>27.42</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -2628,20 +2628,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>012832</t>
+          <t>011555</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南方中证新能源ETF联接C</t>
+          <t>海富通欣利混合C</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7294</v>
+        <v>1.4213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>42.33</v>
+        <v>31.51</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2672,26 +2672,26 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>25.25</v>
+        <v>-9.94</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0827</v>
+        <v>-0.0959</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>10.8</v>
+        <v>15.2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="n">
-        <v>47.9</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -2725,14 +2725,14 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>65.01000000000001</v>
+        <v>12.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -2743,20 +2743,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>000369</t>
+          <t>159687</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>广发全球医疗保健指数人民币(QDII)A</t>
+          <t>亚太精选ETF南方</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.5215</v>
+        <v>1.8816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>58.87</v>
+        <v>64.52</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2787,51 +2787,51 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>101.21</v>
+        <v>90.38</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.8424</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>-1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0.9433</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>-1.5</v>
-      </c>
       <c r="T8" t="n">
-        <v>13.8</v>
+        <v>25.6</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.081</v>
       </c>
       <c r="W8" t="n">
-        <v>83</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2840,14 +2840,14 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>14.51</v>
+        <v>15.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -2858,20 +2858,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>118002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>沪深300ETF易方达</t>
+          <t>易方达标普消费品指数A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.5085</v>
+        <v>2.9343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2883,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>56.13</v>
+        <v>49.23</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>86.97</v>
+        <v>12.27</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5566</v>
+        <v>0.5637</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>20.6</v>
+        <v>9</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.709</v>
+        <v>0.849</v>
       </c>
       <c r="W9" t="n">
-        <v>88</v>
+        <v>75.2</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -2955,11 +2955,11 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>36.33</v>
+        <v>28.4</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -2973,20 +2973,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>515580</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>科技100ETF华泰柏瑞</t>
+          <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.856</v>
+        <v>1.7865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2998,71 +2998,71 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>54.41</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>45.81</v>
+        <v>79.94</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.7566000000000001</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="W10" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="X10" t="n">
         <v>-1</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.5222</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>趋势</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W10" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>多头</t>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>38.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -3088,20 +3088,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>040046</t>
+          <t>510310</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>华安纳斯达克100ETF联接(QDII)A</t>
+          <t>沪深300ETF易方达</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.539099999999999</v>
+        <v>2.4197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3113,15 +3113,15 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>76.09</v>
+        <v>39.29</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>103.65</v>
+        <v>-7.91</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3144,55 +3144,55 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8685</v>
+        <v>-0.1613</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>-1</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>43.3</v>
+        <v>17.7</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.798</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>100</v>
+        <v>79.8</v>
       </c>
       <c r="X11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
       <c r="AA11" t="n">
-        <v>31.24</v>
+        <v>36.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -3203,20 +3203,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>159687</t>
+          <t>006476</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>亚太精选ETF南方</t>
+          <t>南方原油C</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.8249</v>
+        <v>1.7868</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3228,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>61.55</v>
+        <v>49.33</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>107.53</v>
+        <v>75.27</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3259,14 +3259,14 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6979</v>
+        <v>0.3283</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>20.7</v>
+        <v>13.9</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -3285,13 +3285,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1.016</v>
+        <v>2.044</v>
       </c>
       <c r="W12" t="n">
-        <v>98.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>15.3</v>
+        <v>31.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -3318,40 +3318,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>510580</t>
+          <t>000216</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中证500ETF易方达</t>
+          <t>华安黄金ETF联接A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.6571</v>
+        <v>3.2537</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>46.39</v>
+        <v>28.74</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>15.85</v>
+        <v>11.74</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1184</v>
+        <v>-0.0919</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>17.4</v>
+        <v>22.4</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3400,29 +3400,29 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>1.298</v>
+        <v>1.102</v>
       </c>
       <c r="W13" t="n">
-        <v>88.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>38.31</v>
+        <v>25.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.5</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -3442,11 +3442,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7844</v>
+        <v>0.7601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>45.41</v>
+        <v>39.51</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3470,14 +3470,14 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L14" t="n">
-        <v>73.39</v>
+        <v>-12.94</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3489,22 +3489,22 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3076</v>
+        <v>0.0217</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T14" t="n">
         <v>11.2</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1.07</v>
+        <v>1.672</v>
       </c>
       <c r="W14" t="n">
-        <v>46.4</v>
+        <v>42.3</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -3537,7 +3537,7 @@
         <v>53.89</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -3548,32 +3548,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>006476</t>
+          <t>008115</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>南方原油C</t>
+          <t>天弘中证红利低波动100联接C</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.7423</v>
+        <v>1.7246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>43.98</v>
+        <v>40.75</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3585,14 +3585,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-21.99</v>
+        <v>17.74</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3604,14 +3604,14 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0751</v>
+        <v>0.172</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>17.6</v>
+        <v>13.8</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3630,29 +3630,29 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>2.092</v>
+        <v>0.609</v>
       </c>
       <c r="W15" t="n">
-        <v>87.2</v>
+        <v>88.7</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>31.68</v>
+        <v>13.26</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3663,20 +3663,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>050025</t>
+          <t>501060</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>中金中证优选300指数(LOF)A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.6087</v>
+        <v>2.2665</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3688,15 +3688,15 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>71.51000000000001</v>
+        <v>33.16</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>106.05</v>
+        <v>-2.87</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3719,55 +3719,55 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.841</v>
+        <v>0.0362</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>-1</v>
+        <v>1.5</v>
       </c>
       <c r="T16" t="n">
-        <v>37</v>
+        <v>19.1</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.472</v>
+        <v>0.737</v>
       </c>
       <c r="W16" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="X16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>18.73</v>
+        <v>24.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -3778,20 +3778,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>011555</t>
+          <t>012832</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>海富通欣利混合C</t>
+          <t>南方中证新能源ETF联接C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.4358</v>
+        <v>0.6601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3803,15 +3803,15 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>40.26</v>
+        <v>23.54</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -3822,26 +3822,26 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>15.62</v>
+        <v>-7.63</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0643</v>
+        <v>-0.2111</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>1.5</v>
       </c>
       <c r="T17" t="n">
-        <v>12.9</v>
+        <v>18.8</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.283</v>
+        <v>1.541</v>
       </c>
       <c r="W17" t="n">
-        <v>93</v>
+        <v>38.2</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -3875,14 +3875,14 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>12.06</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -3893,20 +3893,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>159928</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>易方达标普消费品指数A</t>
+          <t>消费ETF汇添富</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.9814</v>
+        <v>2.5888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3918,15 +3918,15 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>56.76</v>
+        <v>22.17</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>113.74</v>
+        <v>-3.91</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -3949,43 +3949,43 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.8635</v>
+        <v>0.0149</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>-1.5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>11.4</v>
+        <v>40.2</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.844</v>
+        <v>1.006</v>
       </c>
       <c r="W18" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>28.4</v>
+        <v>52.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>-2.5</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -4008,20 +4008,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>008115</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>天弘中证红利低波动100联接C</t>
+          <t>交银优选回报灵活配置混合C</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.7483</v>
+        <v>1.5515</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>48.71</v>
+        <v>43.87</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -4052,37 +4052,37 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>56.85</v>
+        <v>-7.19</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>买入</t>
         </is>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
       <c r="Q19" t="n">
-        <v>0.4447</v>
+        <v>0.0339</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>15.3</v>
+        <v>19.4</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4090,29 +4090,29 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.507</v>
+        <v>0.061</v>
       </c>
       <c r="W19" t="n">
-        <v>91.2</v>
+        <v>97.7</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>13.26</v>
+        <v>3.91</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -4123,20 +4123,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>000216</t>
+          <t>515580</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>华安黄金ETF联接A</t>
+          <t>科技100ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.413</v>
+        <v>2.7153</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>40.13</v>
+        <v>40.26</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -4167,37 +4167,37 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.79</v>
+        <v>-14.27</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>买入</t>
         </is>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>1</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" t="n">
-        <v>0.2352</v>
+        <v>-0.1298</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T20" t="n">
-        <v>20.1</v>
+        <v>19.2</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -4205,29 +4205,29 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>1.022</v>
+        <v>1.392</v>
       </c>
       <c r="W20" t="n">
-        <v>70.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>25.07</v>
+        <v>38.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
